--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC91626-01F1-7F41-966D-2E73868088C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D359F05B-1D9C-F747-AF41-BA7F4CD9F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2309,9 +2279,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2333,6 +2300,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2342,16 +2315,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14686,7 +14656,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=b19hc7&amp;q=XNYS%3aVRT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -14706,8 +14676,10 @@
     <v>379.935</v>
     <v>133.85</v>
     <v>2.0425</v>
-    <v>5.28</v>
-    <v>2.1524999999999999E-2</v>
+    <v>8.01</v>
+    <v>3.2654000000000002E-2</v>
+    <v>-1.31</v>
+    <v>-5.1719999999999995E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14718,46 +14690,32 @@
     <v>254.48</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46290.718816747656</v>
+    <v>46290.838114166407</v>
     <v>0</v>
     <v>248</v>
-    <v>96470343156</v>
+    <v>97521360942</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>249.18</v>
-    <v>56.706400000000002</v>
+    <v>57.324199999999998</v>
     <v>245.3</v>
-    <v>250.58</v>
+    <v>253.31</v>
+    <v>252</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>2360534</v>
+    <v>4071493</v>
     <v>5124338</v>
     <v>2016</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -14776,7 +14734,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -14786,13 +14744,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -14814,6 +14772,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -14834,6 +14794,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -14843,11 +14804,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -14883,7 +14839,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -14894,13 +14850,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -14994,13 +14953,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15072,6 +15037,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15079,6 +15047,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -15563,18 +15534,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="245"/>
-      <c r="E2" s="244" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="245"/>
-      <c r="H2" s="244" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>318</v>
       </c>
-      <c r="I2" s="245"/>
+      <c r="I2" s="244"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="179" t="s">
@@ -15589,7 +15560,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>98477.94</v>
+        <v>99550.83</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15613,7 +15584,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>98306.94</v>
+        <v>99379.83</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15621,7 +15592,7 @@
       </c>
       <c r="I4" s="205">
         <f>'AVG target price'!C6</f>
-        <v>406.47605820361872</v>
+        <v>409.2368724529826</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -15630,7 +15601,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15652,16 +15623,16 @@
       <c r="B6" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="202" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="202" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>252</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>56.692307692307693</v>
+        <v>57.309954751131222</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15669,7 +15640,7 @@
       </c>
       <c r="I6" s="205">
         <f>'AVG target price'!C8</f>
-        <v>414.00266184562895</v>
+        <v>416.76347609499282</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -15678,14 +15649,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.28</v>
+        <v>8.01</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.55639024390244</v>
+        <v>8.6496097560975613</v>
       </c>
       <c r="H7" s="178" t="str">
         <f>'AVG target price'!B9</f>
@@ -15693,23 +15664,23 @@
       </c>
       <c r="I7" s="206">
         <f>'AVG target price'!C9</f>
-        <v>305.74581729133126</v>
+        <v>307.1262244160132</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-1.31</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2.9427910453853928E-2</v>
+        <v>2.9110756786256829E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B11</f>
@@ -15717,7 +15688,7 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.22015251532975996</v>
+        <v>0.212452032750437</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -15726,23 +15697,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.1524999999999999E-2</v>
+        <v>3.2654000000000002E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.7639077340569877E-2</v>
+        <v>1.7448975563538745E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-5.1719999999999995E-3</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15772,7 +15743,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>8.9791683294756163E-4</v>
+        <v>8.8823970628873711E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -15829,7 +15800,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7364294988298902E-3</v>
+        <v>1.7177154625431048E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -15842,10 +15813,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="246" t="s">
+      <c r="B17" s="245" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="246"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="178" t="s">
         <v>289</v>
       </c>
@@ -15918,14 +15889,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="246" t="s">
+      <c r="B25" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="246"/>
-      <c r="E25" s="244" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="245"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="178" t="s">
@@ -15934,7 +15905,7 @@
       <c r="C26" s="164">
         <v>0.21</v>
       </c>
-      <c r="E26" s="179" t="e" vm="5">
+      <c r="E26" s="179" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="213" cm="1">
@@ -15974,15 +15945,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="241" t="s">
+      <c r="B33" s="240" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="241"/>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16001,24 +15972,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="241"/>
-      <c r="C39" s="241"/>
-      <c r="D39" s="241"/>
-      <c r="E39" s="241"/>
-      <c r="F39" s="241"/>
-      <c r="G39" s="241"/>
-      <c r="H39" s="241"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="241" t="s">
+      <c r="B42" s="240" t="s">
         <v>329</v>
       </c>
-      <c r="C42" s="241"/>
-      <c r="D42" s="241"/>
-      <c r="E42" s="241"/>
-      <c r="F42" s="241"/>
-      <c r="G42" s="241"/>
-      <c r="H42" s="241"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16041,24 +16012,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="241"/>
-      <c r="C49" s="241"/>
-      <c r="D49" s="241"/>
-      <c r="E49" s="241"/>
-      <c r="F49" s="241"/>
-      <c r="G49" s="241"/>
-      <c r="H49" s="241"/>
+      <c r="B49" s="240"/>
+      <c r="C49" s="240"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="240"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="241" t="s">
+      <c r="B52" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="241"/>
-      <c r="D52" s="241"/>
-      <c r="E52" s="241"/>
-      <c r="F52" s="241"/>
-      <c r="G52" s="241"/>
-      <c r="H52" s="241"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16073,28 +16044,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="241"/>
-      <c r="C59" s="241"/>
-      <c r="D59" s="241"/>
-      <c r="E59" s="241"/>
-      <c r="F59" s="241"/>
-      <c r="G59" s="241"/>
-      <c r="H59" s="241"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16164,36 +16135,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="241" t="s">
+      <c r="S2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="241"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="241"/>
-      <c r="X2" s="241"/>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="241"/>
-      <c r="AA2" s="241" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="AB2" s="241"/>
-      <c r="AC2" s="241"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>111</v>
       </c>
@@ -16204,32 +16175,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="239" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="252" t="s">
+      <c r="S4" s="251" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="T4" s="252"/>
+      <c r="U4" s="252"/>
+      <c r="V4" s="252"/>
+      <c r="W4" s="252"/>
+      <c r="X4" s="252"/>
+      <c r="Y4" s="252"/>
+      <c r="Z4" s="252"/>
+      <c r="AA4" s="252"/>
+      <c r="AB4" s="252"/>
+      <c r="AC4" s="252"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -16620,33 +16591,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="240" t="s">
+      <c r="C10" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="252" t="s">
+      <c r="S10" s="251" t="s">
         <v>118</v>
       </c>
-      <c r="T10" s="253"/>
-      <c r="U10" s="253"/>
-      <c r="V10" s="253"/>
-      <c r="W10" s="253"/>
-      <c r="X10" s="253"/>
-      <c r="Y10" s="253"/>
-      <c r="Z10" s="253"/>
-      <c r="AA10" s="253"/>
-      <c r="AB10" s="253"/>
-      <c r="AC10" s="253"/>
+      <c r="T10" s="252"/>
+      <c r="U10" s="252"/>
+      <c r="V10" s="252"/>
+      <c r="W10" s="252"/>
+      <c r="X10" s="252"/>
+      <c r="Y10" s="252"/>
+      <c r="Z10" s="252"/>
+      <c r="AA10" s="252"/>
+      <c r="AB10" s="252"/>
+      <c r="AC10" s="252"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -17033,35 +17004,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
-      <c r="P2" s="241" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="241"/>
-      <c r="R2" s="241"/>
-      <c r="S2" s="241"/>
-      <c r="T2" s="241"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="241"/>
-      <c r="X2" s="241" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="241"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>111</v>
       </c>
@@ -17070,31 +17041,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="239" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="P4" s="253" t="s">
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="P4" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="Q4" s="253"/>
-      <c r="R4" s="253"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="Q4" s="252"/>
+      <c r="R4" s="252"/>
+      <c r="S4" s="252"/>
+      <c r="T4" s="252"/>
+      <c r="U4" s="252"/>
+      <c r="V4" s="252"/>
+      <c r="W4" s="252"/>
+      <c r="X4" s="252"/>
+      <c r="Y4" s="252"/>
+      <c r="Z4" s="252"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17289,32 +17260,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="239" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="239"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="253" t="s">
+      <c r="P9" s="252" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="253"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
-      <c r="T9" s="253"/>
-      <c r="U9" s="253"/>
-      <c r="V9" s="253"/>
-      <c r="W9" s="253"/>
-      <c r="X9" s="253"/>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
+      <c r="Q9" s="252"/>
+      <c r="R9" s="252"/>
+      <c r="S9" s="252"/>
+      <c r="T9" s="252"/>
+      <c r="U9" s="252"/>
+      <c r="V9" s="252"/>
+      <c r="W9" s="252"/>
+      <c r="X9" s="252"/>
+      <c r="Y9" s="252"/>
+      <c r="Z9" s="252"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -17980,31 +17951,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="240" t="s">
+      <c r="C19" s="239" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="E19" s="240"/>
-      <c r="F19" s="240"/>
-      <c r="G19" s="240"/>
-      <c r="H19" s="240"/>
-      <c r="I19" s="240"/>
-      <c r="J19" s="240"/>
-      <c r="K19" s="240"/>
-      <c r="L19" s="240"/>
-      <c r="P19" s="253" t="s">
+      <c r="D19" s="239"/>
+      <c r="E19" s="239"/>
+      <c r="F19" s="239"/>
+      <c r="G19" s="239"/>
+      <c r="H19" s="239"/>
+      <c r="I19" s="239"/>
+      <c r="J19" s="239"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="239"/>
+      <c r="P19" s="252" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="253"/>
-      <c r="R19" s="253"/>
-      <c r="S19" s="253"/>
-      <c r="T19" s="253"/>
-      <c r="U19" s="253"/>
-      <c r="V19" s="253"/>
-      <c r="W19" s="253"/>
-      <c r="X19" s="253"/>
-      <c r="Y19" s="253"/>
-      <c r="Z19" s="253"/>
+      <c r="Q19" s="252"/>
+      <c r="R19" s="252"/>
+      <c r="S19" s="252"/>
+      <c r="T19" s="252"/>
+      <c r="U19" s="252"/>
+      <c r="V19" s="252"/>
+      <c r="W19" s="252"/>
+      <c r="X19" s="252"/>
+      <c r="Y19" s="252"/>
+      <c r="Z19" s="252"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="s">
@@ -18652,60 +18623,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
-      <c r="P3" s="239"/>
-      <c r="Q3" s="239"/>
-      <c r="R3" s="239"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="239"/>
-      <c r="U3" s="239"/>
-      <c r="V3" s="239"/>
-      <c r="W3" s="239"/>
-      <c r="X3" s="239"/>
-      <c r="Y3" s="239"/>
-      <c r="Z3" s="239"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="239" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="239"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="239"/>
-      <c r="S5" s="239"/>
-      <c r="T5" s="239"/>
-      <c r="U5" s="239"/>
-      <c r="V5" s="239"/>
-      <c r="W5" s="239"/>
-      <c r="X5" s="239"/>
-      <c r="Y5" s="239"/>
-      <c r="Z5" s="239"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18891,30 +18862,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="239"/>
-      <c r="Q11" s="239"/>
-      <c r="R11" s="239"/>
-      <c r="S11" s="239"/>
-      <c r="T11" s="239"/>
-      <c r="U11" s="239"/>
-      <c r="V11" s="239"/>
-      <c r="W11" s="239"/>
-      <c r="X11" s="239"/>
-      <c r="Y11" s="239"/>
-      <c r="Z11" s="239"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="253"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19156,18 +19127,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="239" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19380,23 +19351,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="239"/>
-      <c r="C25" s="239"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="239" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="239"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19588,18 +19559,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="240" t="s">
+      <c r="C33" s="239" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
-      <c r="I33" s="240"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
-      <c r="L33" s="240"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="239"/>
+      <c r="F33" s="239"/>
+      <c r="G33" s="239"/>
+      <c r="H33" s="239"/>
+      <c r="I33" s="239"/>
+      <c r="J33" s="239"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19783,18 +19754,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="239" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="239"/>
+      <c r="F40" s="239"/>
+      <c r="G40" s="239"/>
+      <c r="H40" s="239"/>
+      <c r="I40" s="239"/>
+      <c r="J40" s="239"/>
+      <c r="K40" s="239"/>
+      <c r="L40" s="239"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20058,6 +20029,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20065,12 +20042,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20108,60 +20079,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
-      <c r="S2" s="239"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="239"/>
-      <c r="V2" s="239"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="239"/>
-      <c r="Y2" s="239"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="239"/>
-      <c r="AB2" s="239"/>
-      <c r="AC2" s="239"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="S4" s="239"/>
-      <c r="T4" s="239"/>
-      <c r="U4" s="239"/>
-      <c r="V4" s="239"/>
-      <c r="W4" s="239"/>
-      <c r="X4" s="239"/>
-      <c r="Y4" s="239"/>
-      <c r="Z4" s="239"/>
-      <c r="AA4" s="239"/>
-      <c r="AB4" s="239"/>
-      <c r="AC4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20524,18 +20495,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="239" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="240"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20628,18 +20599,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="239" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20831,18 +20802,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="239" t="s">
         <v>255</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
+      <c r="D25" s="239"/>
+      <c r="E25" s="239"/>
+      <c r="F25" s="239"/>
+      <c r="G25" s="239"/>
+      <c r="H25" s="239"/>
+      <c r="I25" s="239"/>
+      <c r="J25" s="239"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20980,18 +20951,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="240" t="s">
+      <c r="C31" s="239" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="240"/>
-      <c r="G31" s="240"/>
-      <c r="H31" s="240"/>
-      <c r="I31" s="240"/>
-      <c r="J31" s="240"/>
-      <c r="K31" s="240"/>
-      <c r="L31" s="240"/>
+      <c r="D31" s="239"/>
+      <c r="E31" s="239"/>
+      <c r="F31" s="239"/>
+      <c r="G31" s="239"/>
+      <c r="H31" s="239"/>
+      <c r="I31" s="239"/>
+      <c r="J31" s="239"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21130,16 +21101,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21202,10 +21173,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="240" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="241"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21222,7 +21193,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21231,7 +21202,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>98477.94</v>
+        <v>99550.83</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21290,10 +21261,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="241" t="s">
+      <c r="B15" s="240" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="241"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21301,7 +21272,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.8988954025293751E-2</v>
+        <v>2.8685493131434293E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21310,7 +21281,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97101104597470622</v>
+        <v>0.97131450686856569</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21337,7 +21308,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1406770155561235</v>
+        <v>0.14070690721282092</v>
       </c>
     </row>
   </sheetData>
@@ -21382,60 +21353,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
-      <c r="P3" s="239"/>
-      <c r="Q3" s="239"/>
-      <c r="R3" s="239"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="239"/>
-      <c r="U3" s="239"/>
-      <c r="V3" s="239"/>
-      <c r="W3" s="239"/>
-      <c r="X3" s="239"/>
-      <c r="Y3" s="239"/>
-      <c r="Z3" s="239"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="239" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="239"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="239"/>
-      <c r="S5" s="239"/>
-      <c r="T5" s="239"/>
-      <c r="U5" s="239"/>
-      <c r="V5" s="239"/>
-      <c r="W5" s="239"/>
-      <c r="X5" s="239"/>
-      <c r="Y5" s="239"/>
-      <c r="Z5" s="239"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21681,10 +21652,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="241" t="s">
+      <c r="B13" s="240" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="241"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21704,10 +21675,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="241" t="s">
+      <c r="B18" s="240" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="241"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21821,37 +21792,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="239" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22071,18 +22042,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22276,18 +22247,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="239" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="239"/>
+      <c r="G17" s="239"/>
+      <c r="H17" s="239"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22421,18 +22392,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="240" t="s">
+      <c r="C22" s="239" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="240"/>
-      <c r="E22" s="240"/>
-      <c r="F22" s="240"/>
-      <c r="G22" s="240"/>
-      <c r="H22" s="240"/>
-      <c r="I22" s="240"/>
-      <c r="J22" s="240"/>
-      <c r="K22" s="240"/>
-      <c r="L22" s="240"/>
+      <c r="D22" s="239"/>
+      <c r="E22" s="239"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22516,18 +22487,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="240" t="s">
+      <c r="C27" s="239" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="E27" s="240"/>
-      <c r="F27" s="240"/>
-      <c r="G27" s="240"/>
-      <c r="H27" s="240"/>
-      <c r="I27" s="240"/>
-      <c r="J27" s="240"/>
-      <c r="K27" s="240"/>
-      <c r="L27" s="240"/>
+      <c r="D27" s="239"/>
+      <c r="E27" s="239"/>
+      <c r="F27" s="239"/>
+      <c r="G27" s="239"/>
+      <c r="H27" s="239"/>
+      <c r="I27" s="239"/>
+      <c r="J27" s="239"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="239"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22797,10 +22768,10 @@
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="241" t="s">
+      <c r="B38" s="240" t="s">
         <v>201</v>
       </c>
-      <c r="C38" s="241"/>
+      <c r="C38" s="240"/>
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -22843,8 +22814,8 @@
         <v>397</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/(1+C40)^5-G31+G32</f>
-        <v>147841.59798428035</v>
+        <f>C42/(1+C40)^5</f>
+        <v>148926.59798428035</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -22853,7 +22824,7 @@
       </c>
       <c r="C44" s="108">
         <f>SUM(H9:K9)+C43</f>
-        <v>159574.09087402216</v>
+        <v>160659.09087402216</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22880,7 +22851,7 @@
       </c>
       <c r="C47" s="94">
         <f>C44+C45-C46</f>
-        <v>159745.09087402216</v>
+        <v>160830.09087402216</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -22898,14 +22869,14 @@
       </c>
       <c r="C49" s="238">
         <f>C47/C48</f>
-        <v>406.47605820361872</v>
+        <v>409.2368724529826</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="241" t="s">
+      <c r="B51" s="240" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="241"/>
+      <c r="C51" s="240"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -22961,10 +22932,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="241" t="s">
+      <c r="B59" s="240" t="s">
         <v>315</v>
       </c>
-      <c r="C59" s="241"/>
+      <c r="C59" s="240"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -23006,8 +22977,8 @@
         <v>397</v>
       </c>
       <c r="C64" s="24">
-        <f>C63/(1+C61)^5-G31+G32</f>
-        <v>150799.55321559036</v>
+        <f>C63/(1+C61)^5</f>
+        <v>151884.55321559036</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -23016,7 +22987,7 @@
       </c>
       <c r="C65" s="108">
         <f>SUM(H9:K9)+C64</f>
-        <v>162532.04610533218</v>
+        <v>163617.04610533218</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23043,7 +23014,7 @@
       </c>
       <c r="C68" s="94">
         <f>C65+C66-C67</f>
-        <v>162703.04610533218</v>
+        <v>163788.04610533218</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -23061,7 +23032,7 @@
       </c>
       <c r="C70" s="238">
         <f>C68/C69</f>
-        <v>414.00266184562895</v>
+        <v>416.76347609499282</v>
       </c>
     </row>
   </sheetData>
@@ -23113,10 +23084,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="240" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="241"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23134,7 +23105,7 @@
       </c>
       <c r="C6" s="133">
         <f>Multiples!C49</f>
-        <v>406.47605820361872</v>
+        <v>409.2368724529826</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23152,7 +23123,7 @@
       </c>
       <c r="C8" s="133">
         <f>Multiples!C70</f>
-        <v>414.00266184562895</v>
+        <v>416.76347609499282</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23161,7 +23132,7 @@
       </c>
       <c r="C9" s="238">
         <f>AVERAGE(C5:C8)</f>
-        <v>305.74581729133126</v>
+        <v>307.1262244160132</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23170,7 +23141,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23179,7 +23150,7 @@
       </c>
       <c r="C11" s="149">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.22015251532975996</v>
+        <v>0.212452032750437</v>
       </c>
     </row>
   </sheetData>
@@ -23235,37 +23206,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="239" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23378,18 +23349,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="239"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23510,18 +23481,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="240" t="s">
+      <c r="C14" s="239" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="240"/>
-      <c r="E14" s="240"/>
-      <c r="F14" s="240"/>
-      <c r="G14" s="240"/>
-      <c r="H14" s="240"/>
-      <c r="I14" s="240"/>
-      <c r="J14" s="240"/>
-      <c r="K14" s="240"/>
-      <c r="L14" s="240"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="239"/>
+      <c r="F14" s="239"/>
+      <c r="G14" s="239"/>
+      <c r="H14" s="239"/>
+      <c r="I14" s="239"/>
+      <c r="J14" s="239"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23611,10 +23582,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="241" t="s">
+      <c r="B20" s="240" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="241"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23715,60 +23686,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
-      <c r="P3" s="239"/>
-      <c r="Q3" s="239"/>
-      <c r="R3" s="239"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="239"/>
-      <c r="U3" s="239"/>
-      <c r="V3" s="239"/>
-      <c r="W3" s="239"/>
-      <c r="X3" s="239"/>
-      <c r="Y3" s="239"/>
-      <c r="Z3" s="239"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="239" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="239"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="239"/>
-      <c r="S5" s="239"/>
-      <c r="T5" s="239"/>
-      <c r="U5" s="239"/>
-      <c r="V5" s="239"/>
-      <c r="W5" s="239"/>
-      <c r="X5" s="239"/>
-      <c r="Y5" s="239"/>
-      <c r="Z5" s="239"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24008,7 +23979,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24074,7 +24045,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>96473.3</v>
+        <v>97524.35</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24101,7 +24072,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>96302.3</v>
+        <v>97353.35</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24185,16 +24156,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30735,7 +30706,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30806,7 +30777,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31916,7 +31887,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>56.692307692307693</v>
+        <v>57.309954751131222</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -31953,7 +31924,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.55639024390244</v>
+        <v>8.6496097560975613</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32014,7 +31985,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>20.276019335855402</v>
+        <v>20.496920975199664</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32075,7 +32046,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>98477.94</v>
+        <v>99550.83</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32136,7 +32107,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>98306.94</v>
+        <v>99379.83</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32173,7 +32144,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.5633222996515688</v>
+        <v>8.6567796167247391</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32210,7 +32181,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>45.281870105941962</v>
+        <v>45.776061722708427</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32345,7 +32316,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>33.981345755693582</v>
+        <v>34.351563146997933</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32382,7 +32353,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>24.884592027469033</v>
+        <v>25.156174379033949</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32419,7 +32390,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>2.9427910453853928E-2</v>
+        <v>2.9110756786256829E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32456,7 +32427,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7639077340569877E-2</v>
+        <v>1.7448975563538745E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32493,7 +32464,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>8.9791683294756163E-4</v>
+        <v>8.8823970628873711E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32567,7 +32538,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>8.732920286512898E-4</v>
+        <v>8.6388029110354982E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33070,7 +33041,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7364294988298902E-3</v>
+        <v>1.7177154625431048E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34564,15 +34535,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="240" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="241"/>
-      <c r="E4" s="241" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34580,7 +34551,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34596,7 +34567,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>98477.94</v>
+        <v>99550.83</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34616,7 +34587,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>98306.94</v>
+        <v>99379.83</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34636,7 +34607,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>56.692307692307693</v>
+        <v>57.309954751131222</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34656,7 +34627,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.55639024390244</v>
+        <v>8.6496097560975613</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34676,7 +34647,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.276019335855402</v>
+        <v>20.496920975199664</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34696,7 +34667,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.5633222996515688</v>
+        <v>8.6567796167247391</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34705,18 +34676,18 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.281870105941962</v>
+        <v>45.776061722708427</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="241" t="s">
+      <c r="B15" s="240" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="241"/>
-      <c r="E15" s="241" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>239</v>
       </c>
-      <c r="F15" s="241"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34767,14 +34738,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="241" t="s">
+      <c r="B21" s="240" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="241"/>
-      <c r="E21" s="241" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>242</v>
       </c>
-      <c r="F21" s="241"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34843,14 +34814,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="241" t="s">
+      <c r="B29" s="240" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="241"/>
-      <c r="E29" s="241" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>249</v>
       </c>
-      <c r="F29" s="241"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34926,14 +34897,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="241" t="s">
+      <c r="B37" s="240" t="s">
         <v>261</v>
       </c>
-      <c r="C37" s="241"/>
-      <c r="E37" s="241" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="241"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34941,7 +34912,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7639077340569877E-2</v>
+        <v>1.7448975563538745E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -34957,7 +34928,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>2.9427910453853928E-2</v>
+        <v>2.9110756786256829E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -34973,7 +34944,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.9791683294756163E-4</v>
+        <v>8.8823970628873711E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -34998,18 +34969,18 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.732920286512898E-4</v>
+        <v>8.6388029110354982E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="241" t="s">
+      <c r="B45" s="240" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="241"/>
-      <c r="E45" s="241" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>278</v>
       </c>
-      <c r="F45" s="241"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35042,18 +35013,18 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7364294988298902E-3</v>
+        <v>1.7177154625431048E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="241" t="s">
+      <c r="B51" s="240" t="s">
         <v>275</v>
       </c>
-      <c r="C51" s="241"/>
-      <c r="E51" s="241" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>296</v>
       </c>
-      <c r="F51" s="241"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35221,7 +35192,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>250.58</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35250,7 +35221,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>98477.94</v>
+        <v>99550.83</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35279,7 +35250,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>98306.94</v>
+        <v>99379.83</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35308,7 +35279,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>56.692307692307693</v>
+        <v>57.309954751131222</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35337,7 +35308,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.55639024390244</v>
+        <v>8.6496097560975613</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35366,7 +35337,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.276019335855402</v>
+        <v>20.496920975199664</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35395,7 +35366,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.5633222996515688</v>
+        <v>8.6567796167247391</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35424,7 +35395,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.281870105941962</v>
+        <v>45.776061722708427</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36197,7 +36168,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7639077340569877E-2</v>
+        <v>1.7448975563538745E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36226,7 +36197,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>2.9427910453853928E-2</v>
+        <v>2.9110756786256829E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36255,7 +36226,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.9791683294756163E-4</v>
+        <v>8.8823970628873711E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36313,7 +36284,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.732920286512898E-4</v>
+        <v>8.6388029110354982E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36549,7 +36520,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7364294988298902E-3</v>
+        <v>1.7177154625431048E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37101,14 +37072,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37175,19 +37146,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37214,19 +37185,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37253,19 +37224,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37292,19 +37263,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37331,19 +37302,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37370,19 +37341,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37409,22 +37380,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37451,22 +37422,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37515,22 +37486,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37558,22 +37529,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37601,22 +37572,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -37644,22 +37615,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="250">
+      <c r="C32" s="246">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="F32" s="250">
+      <c r="D32" s="247"/>
+      <c r="F32" s="246">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="251"/>
+      <c r="G32" s="247"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -37687,25 +37658,43 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="250">
+      <c r="C34" s="246">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="F34" s="250">
+      <c r="D34" s="247"/>
+      <c r="F34" s="246">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="251"/>
+      <c r="G34" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -37716,24 +37705,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D359F05B-1D9C-F747-AF41-BA7F4CD9F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0923C746-0084-B743-91DA-4D7F4461BEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="405">
   <si>
     <t>Ticker</t>
   </si>
@@ -1352,6 +1352,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -2300,12 +2315,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2313,6 +2322,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14675,11 +14690,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>133.85</v>
-    <v>2.0425</v>
-    <v>8.01</v>
-    <v>3.2654000000000002E-2</v>
-    <v>-1.31</v>
-    <v>-5.1719999999999995E-3</v>
+    <v>2.0379999999999998</v>
+    <v>7.98</v>
+    <v>3.2531999999999998E-2</v>
+    <v>2.4799999999999999E-2</v>
+    <v>9.7919999999999998E-5</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14687,24 +14702,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>254.48</v>
+    <v>254.5</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46290.838114166407</v>
+    <v>46290.999964872659</v>
     <v>0</v>
     <v>248</v>
-    <v>97521360942</v>
+    <v>97509811296</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>249.18</v>
-    <v>57.324199999999998</v>
+    <v>55.511699999999998</v>
     <v>245.3</v>
-    <v>253.31</v>
-    <v>252</v>
+    <v>253.28</v>
+    <v>253.3048</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>4071493</v>
+    <v>4134525</v>
     <v>5124338</v>
     <v>2016</v>
   </rv>
@@ -14727,19 +14742,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14961,9 +14976,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15560,7 +15575,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>99550.83</v>
+        <v>99539.04</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15584,7 +15599,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>99379.83</v>
+        <v>99368.04</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15601,7 +15616,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15625,14 +15640,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>252</v>
+        <v>253.3048</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>57.309954751131222</v>
+        <v>57.303167420814482</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15649,22 +15664,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.01</v>
+        <v>7.98</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.6496097560975613</v>
+        <v>8.6485853658536591</v>
       </c>
       <c r="H7" s="178" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="206">
-        <f>'AVG target price'!C9</f>
-        <v>307.1262244160132</v>
+        <f>'AVG target price'!C10</f>
+        <v>300.34182473809454</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -15673,22 +15688,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.31</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2.9110756786256829E-2</v>
+        <v>2.9114204838624123E-2</v>
       </c>
       <c r="H8" s="178" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="207">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>0.212452032750437</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.18580947859323493</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -15697,14 +15712,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.2654000000000002E-2</v>
+        <v>3.2531999999999998E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.7448975563538745E-2</v>
+        <v>1.7451042324699937E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -15713,7 +15728,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.1719999999999995E-3</v>
+        <v>9.7919999999999998E-5</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15743,7 +15758,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>8.8823970628873711E-4</v>
+        <v>8.883449147188882E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -15768,7 +15783,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0425</v>
+        <v>2.0379999999999998</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15800,7 +15815,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7177154625431048E-3</v>
+        <v>1.7179189190492496E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -15910,7 +15925,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -15925,7 +15940,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16054,18 +16069,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -20029,12 +20044,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20042,6 +20051,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21101,16 +21116,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21193,7 +21208,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21202,7 +21217,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>99550.83</v>
+        <v>99539.04</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21220,7 +21235,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21229,7 +21244,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0425</v>
+        <v>2.0379999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21272,7 +21287,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.8685493131434293E-2</v>
+        <v>2.8688793337642508E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21281,7 +21296,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97131450686856569</v>
+        <v>0.97131120666235748</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21299,7 +21314,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14353250000000001</v>
+        <v>0.14354999999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21308,7 +21323,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14070690721282092</v>
+        <v>0.14072358008037544</v>
       </c>
     </row>
   </sheetData>
@@ -21770,7 +21785,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -22739,7 +22754,7 @@
         <v>58.08487793028057</v>
       </c>
       <c r="D35" s="144">
-        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
         <v>-52.155553154543689</v>
       </c>
       <c r="E35" s="144">
@@ -22762,285 +22777,421 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="C36" s="144">
+        <f>C33/C6</f>
+        <v>2.3055622248899557</v>
+      </c>
+      <c r="D36" s="144">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>1.4219044272663386</v>
+      </c>
+      <c r="E36" s="144">
+        <f t="shared" si="14"/>
+        <v>3.0162581961241441</v>
+      </c>
+      <c r="F36" s="144">
+        <f t="shared" si="14"/>
+        <v>5.685654018971543</v>
+      </c>
+      <c r="G36" s="145">
+        <f t="shared" si="14"/>
+        <v>6.2982316715542526</v>
+      </c>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="240" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="240" t="s">
         <v>201</v>
       </c>
-      <c r="C38" s="240"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="240"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>8555.1051342307201</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C40" s="135">
+      <c r="C41" s="135">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.115</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>256653.15402692161</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>256653.15402692161</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C40)^5</f>
+      <c r="C44" s="24">
+        <f>C43/(1+C41)^5</f>
         <v>148926.59798428035</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="C44" s="108">
-        <f>SUM(H9:K9)+C43</f>
+      <c r="C45" s="108">
+        <f>SUM(H9:K9)+C44</f>
         <v>160659.09087402216</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC105</f>
         <v>3111</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C47" s="88">
         <f>Statement!AC106</f>
         <v>2940</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C47" s="94">
-        <f>C44+C45-C46</f>
+      <c r="C48" s="94">
+        <f>C45+C46-C47</f>
         <v>160830.09087402216</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC77</f>
         <v>393</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="C49" s="238">
-        <f>C47/C48</f>
+      <c r="C50" s="238">
+        <f>C48/C49</f>
         <v>409.2368724529826</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="240" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="240"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="240"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>32904.250516271997</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C53" s="135">
+      <c r="C54" s="135">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="C54" s="105">
+      <c r="C55" s="105">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>390.92180391000005</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>420.8546336781892</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="238">
-        <f>C56/(1+C53)^5</f>
+      <c r="C58" s="238">
+        <f>C57/(1+C54)^5</f>
         <v>238.80422150261779</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="240" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="240" t="s">
         <v>315</v>
       </c>
-      <c r="C59" s="240"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="240"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>7698.5516509805393</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C61" s="135">
+      <c r="C62" s="135">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.115</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>261750.75613333835</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>261750.75613333835</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C64" s="24">
-        <f>C63/(1+C61)^5</f>
+      <c r="C65" s="24">
+        <f>C64/(1+C62)^5</f>
         <v>151884.55321559036</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="C65" s="108">
-        <f>SUM(H9:K9)+C64</f>
+      <c r="C66" s="108">
+        <f>SUM(H9:K9)+C65</f>
         <v>163617.04610533218</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C67" s="88">
         <f>Statement!AC105</f>
         <v>3111</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C67" s="88">
+      <c r="C68" s="88">
         <f>Statement!AC106</f>
         <v>2940</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C68" s="94">
-        <f>C65+C66-C67</f>
+      <c r="C69" s="94">
+        <f>C66+C67-C68</f>
         <v>163788.04610533218</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC77</f>
         <v>393</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="237" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="C70" s="238">
-        <f>C68/C69</f>
+      <c r="C71" s="238">
+        <f>C69/C70</f>
         <v>416.76347609499282</v>
       </c>
     </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="240" t="s">
+        <v>401</v>
+      </c>
+      <c r="C73" s="240"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>32904.250516271997</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="135">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="C76" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>164521.25258135999</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C78" s="24">
+        <f>C77/(1+C75)^5</f>
+        <v>95465.767938641235</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="108">
+        <f>SUM(H9:K9)+C78</f>
+        <v>107198.26082838303</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C80" s="88">
+        <f>Statement!AC105</f>
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C81" s="88">
+        <f>Statement!AC106</f>
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C82" s="94">
+        <f>C79+C80-C81</f>
+        <v>107369.26082838303</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC77</f>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="237" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="238">
+        <f>C82/C83</f>
+        <v>273.20422602641992</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -23057,7 +23208,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -23104,7 +23255,7 @@
         <v>212</v>
       </c>
       <c r="C6" s="133">
-        <f>Multiples!C49</f>
+        <f>Multiples!C50</f>
         <v>409.2368724529826</v>
       </c>
     </row>
@@ -23113,7 +23264,7 @@
         <v>213</v>
       </c>
       <c r="C7" s="133">
-        <f>Multiples!C57</f>
+        <f>Multiples!C58</f>
         <v>238.80422150261779</v>
       </c>
     </row>
@@ -23122,35 +23273,44 @@
         <v>316</v>
       </c>
       <c r="C8" s="133">
-        <f>Multiples!C70</f>
+        <f>Multiples!C71</f>
         <v>416.76347609499282</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="133">
+        <f>Multiples!C84</f>
+        <v>273.20422602641992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="237" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="238">
-        <f>AVERAGE(C5:C8)</f>
-        <v>307.1262244160132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="133">
-        <f ca="1">Overview!C5</f>
-        <v>253.31</v>
+      <c r="C10" s="238">
+        <f>AVERAGE(C5:C9)</f>
+        <v>300.34182473809454</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="133">
+        <f ca="1">Overview!C5</f>
+        <v>253.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="149">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.212452032750437</v>
+      <c r="C12" s="149">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>0.18580947859323493</v>
       </c>
     </row>
   </sheetData>
@@ -23979,7 +24139,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24045,7 +24205,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>97524.35</v>
+        <v>97512.8</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24072,7 +24232,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>97353.35</v>
+        <v>97341.8</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24156,16 +24316,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30706,7 +30866,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30777,7 +30937,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31887,7 +32047,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>57.309954751131222</v>
+        <v>57.303167420814482</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -31924,7 +32084,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.6496097560975613</v>
+        <v>8.6485853658536591</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -31985,7 +32145,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>20.496920975199664</v>
+        <v>20.494493484657418</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32046,7 +32206,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>99550.83</v>
+        <v>99539.04</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32107,7 +32267,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>99379.83</v>
+        <v>99368.04</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32144,7 +32304,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.6567796167247391</v>
+        <v>8.6557526132404181</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32181,7 +32341,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>45.776061722708427</v>
+        <v>45.7706310456011</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32316,7 +32476,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>34.351563146997933</v>
+        <v>34.347494824016557</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32353,7 +32513,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>25.156174379033949</v>
+        <v>25.153189957588179</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32390,7 +32550,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>2.9110756786256829E-2</v>
+        <v>2.9114204838624123E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32427,7 +32587,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7448975563538745E-2</v>
+        <v>1.7451042324699937E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32464,7 +32624,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>8.8823970628873711E-4</v>
+        <v>8.883449147188882E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32538,7 +32698,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>8.6388029110354982E-4</v>
+        <v>8.6398261425868689E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33041,7 +33201,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7177154625431048E-3</v>
+        <v>1.7179189190492496E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34551,7 +34711,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34567,7 +34727,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99550.83</v>
+        <v>99539.04</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34587,7 +34747,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99379.83</v>
+        <v>99368.04</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34607,7 +34767,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.309954751131222</v>
+        <v>57.303167420814482</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34627,7 +34787,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6496097560975613</v>
+        <v>8.6485853658536591</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34647,7 +34807,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.496920975199664</v>
+        <v>20.494493484657418</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34667,7 +34827,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.6567796167247391</v>
+        <v>8.6557526132404181</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34676,7 +34836,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.776061722708427</v>
+        <v>45.7706310456011</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34912,7 +35072,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7448975563538745E-2</v>
+        <v>1.7451042324699937E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -34928,7 +35088,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>2.9110756786256829E-2</v>
+        <v>2.9114204838624123E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -34944,7 +35104,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.8823970628873711E-4</v>
+        <v>8.883449147188882E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -34969,7 +35129,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6388029110354982E-4</v>
+        <v>8.6398261425868689E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35013,7 +35173,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7177154625431048E-3</v>
+        <v>1.7179189190492496E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35192,7 +35352,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>253.31</v>
+        <v>253.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35221,7 +35381,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99550.83</v>
+        <v>99539.04</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35250,7 +35410,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99379.83</v>
+        <v>99368.04</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35279,7 +35439,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.309954751131222</v>
+        <v>57.303167420814482</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35308,7 +35468,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6496097560975613</v>
+        <v>8.6485853658536591</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35337,7 +35497,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.496920975199664</v>
+        <v>20.494493484657418</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35366,7 +35526,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.6567796167247391</v>
+        <v>8.6557526132404181</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35395,7 +35555,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.776061722708427</v>
+        <v>45.7706310456011</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36168,7 +36328,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7448975563538745E-2</v>
+        <v>1.7451042324699937E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36197,7 +36357,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>2.9110756786256829E-2</v>
+        <v>2.9114204838624123E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36226,7 +36386,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.8823970628873711E-4</v>
+        <v>8.883449147188882E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36284,7 +36444,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6388029110354982E-4</v>
+        <v>8.6398261425868689E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36520,7 +36680,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7177154625431048E-3</v>
+        <v>1.7179189190492496E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37072,14 +37232,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37146,19 +37306,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37185,19 +37345,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37224,19 +37384,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37263,19 +37423,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37302,19 +37462,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37341,19 +37501,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37380,22 +37540,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37422,22 +37582,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37486,22 +37646,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37529,22 +37689,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37572,22 +37732,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="250"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -37615,22 +37775,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="246">
+      <c r="C32" s="249">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="247"/>
-      <c r="F32" s="246">
+      <c r="D32" s="250"/>
+      <c r="F32" s="249">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="247"/>
+      <c r="G32" s="250"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -37658,43 +37818,25 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="246">
+      <c r="C34" s="249">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="247"/>
-      <c r="F34" s="246">
+      <c r="D34" s="250"/>
+      <c r="F34" s="249">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="247"/>
+      <c r="G34" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -37705,6 +37847,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0923C746-0084-B743-91DA-4D7F4461BEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C301D19E-936F-0C47-8BE3-534F6BD4B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="406">
   <si>
     <t>Ticker</t>
   </si>
@@ -1367,6 +1367,9 @@
   </si>
   <si>
     <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2294,18 +2297,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2313,6 +2304,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2330,10 +2324,19 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -14689,12 +14692,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
-    <v>133.85</v>
-    <v>2.0379999999999998</v>
-    <v>7.98</v>
-    <v>3.2531999999999998E-2</v>
-    <v>2.4799999999999999E-2</v>
-    <v>9.7919999999999998E-5</v>
+    <v>141.4</v>
+    <v>2.0444</v>
+    <v>4.3499999999999996</v>
+    <v>1.7825000000000001E-2</v>
+    <v>0.76</v>
+    <v>3.0599999999999998E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14702,25 +14705,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>254.5</v>
+    <v>254.13</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46290.999964872659</v>
+    <v>46294.962513402344</v>
     <v>0</v>
-    <v>248</v>
-    <v>97509811296</v>
+    <v>246.84</v>
+    <v>95627218998</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>249.18</v>
-    <v>55.511699999999998</v>
-    <v>245.3</v>
-    <v>253.28</v>
-    <v>253.3048</v>
+    <v>251.38</v>
+    <v>56.210799999999999</v>
+    <v>244.04</v>
+    <v>248.39</v>
+    <v>249.1</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>4134525</v>
-    <v>5124338</v>
+    <v>3293269</v>
+    <v>5123818</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14742,19 +14745,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.15</v>
+    <v>2.8630000000000001E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>52.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.13</v>
+    <v>52.4</v>
+    <v>52.55</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14976,9 +14979,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15549,18 +15552,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>318</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="240"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="179" t="s">
@@ -15575,7 +15578,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>99539.04</v>
+        <v>97617.26999999999</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15599,7 +15602,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>99368.04</v>
+        <v>97446.26999999999</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15616,7 +15619,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15640,14 +15643,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>253.3048</v>
+        <v>249.1</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>57.303167420814482</v>
+        <v>56.196832579185518</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15664,22 +15667,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>7.98</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.6485853658536591</v>
-      </c>
-      <c r="H7" s="178" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="206">
-        <f>'AVG target price'!C10</f>
-        <v>300.34182473809454</v>
+        <v>8.4816097560975603</v>
+      </c>
+      <c r="H7" s="179" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="205">
+        <f>'AVG target price'!C9</f>
+        <v>273.20422602641992</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -15688,22 +15691,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>2.4799999999999999E-2</v>
+        <v>0.76</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2.9114204838624123E-2</v>
+        <v>2.9687369868057163E-2</v>
       </c>
       <c r="H8" s="178" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="207">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>0.18580947859323493</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="206">
+        <f>'AVG target price'!C10</f>
+        <v>300.34182473809454</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -15712,14 +15715,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.2531999999999998E-2</v>
+        <v>1.7825000000000001E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.7451042324699937E-2</v>
+        <v>1.7794597206006683E-2</v>
+      </c>
+      <c r="H9" s="178" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="207">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.20915425233743129</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -15728,7 +15739,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>9.7919999999999998E-5</v>
+        <v>3.0599999999999998E-3</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15737,13 +15748,6 @@
         <f ca="1">Statement!AC158</f>
         <v>0</v>
       </c>
-      <c r="H10" s="178" t="s">
-        <v>359</v>
-      </c>
-      <c r="I10" s="206">
-        <f>DDM!C26</f>
-        <v>2.1</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="179" t="s">
@@ -15758,7 +15762,14 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>8.883449147188882E-4</v>
+        <v>9.0583356817907333E-4</v>
+      </c>
+      <c r="H11" s="178" t="s">
+        <v>359</v>
+      </c>
+      <c r="I11" s="206">
+        <f>DDM!C26</f>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -15767,7 +15778,7 @@
       </c>
       <c r="C12" s="203" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>133.85</v>
+        <v>141.4</v>
       </c>
       <c r="E12" s="179" t="s">
         <v>98</v>
@@ -15783,7 +15794,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0379999999999998</v>
+        <v>2.0444</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15792,6 +15803,13 @@
         <f>Statement!AC123</f>
         <v>0.36422866750735605</v>
       </c>
+      <c r="H13" s="178" t="s">
+        <v>405</v>
+      </c>
+      <c r="I13" s="207">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.44500000000000001</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="180" t="s">
@@ -15799,7 +15817,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5124338</v>
+        <v>5123818</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15815,7 +15833,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7179189190492496E-3</v>
+        <v>1.7517392158170374E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -15828,10 +15846,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="241" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="178" t="s">
         <v>289</v>
       </c>
@@ -15904,14 +15922,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="241" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="178" t="s">
@@ -15925,7 +15943,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -15940,7 +15958,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -15960,15 +15978,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="132" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -15987,24 +16005,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="240"/>
-      <c r="C39" s="240"/>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="132"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="132"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="240" t="s">
+      <c r="B42" s="132" t="s">
         <v>329</v>
       </c>
-      <c r="C42" s="240"/>
-      <c r="D42" s="240"/>
-      <c r="E42" s="240"/>
-      <c r="F42" s="240"/>
-      <c r="G42" s="240"/>
-      <c r="H42" s="240"/>
+      <c r="C42" s="132"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16027,24 +16045,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="240"/>
-      <c r="C49" s="240"/>
-      <c r="D49" s="240"/>
-      <c r="E49" s="240"/>
-      <c r="F49" s="240"/>
-      <c r="G49" s="240"/>
-      <c r="H49" s="240"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="240" t="s">
+      <c r="B52" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="240"/>
-      <c r="D52" s="240"/>
-      <c r="E52" s="240"/>
-      <c r="F52" s="240"/>
-      <c r="G52" s="240"/>
-      <c r="H52" s="240"/>
+      <c r="C52" s="132"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="132"/>
+      <c r="F52" s="132"/>
+      <c r="G52" s="132"/>
+      <c r="H52" s="132"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16059,28 +16077,22 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="240"/>
-      <c r="C59" s="240"/>
-      <c r="D59" s="240"/>
-      <c r="E59" s="240"/>
-      <c r="F59" s="240"/>
-      <c r="G59" s="240"/>
-      <c r="H59" s="240"/>
+      <c r="B59" s="132"/>
+      <c r="C59" s="132"/>
+      <c r="D59" s="132"/>
+      <c r="E59" s="132"/>
+      <c r="F59" s="132"/>
+      <c r="G59" s="132"/>
+      <c r="H59" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16150,36 +16162,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>111</v>
       </c>
@@ -16190,32 +16202,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="248" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="251" t="s">
+      <c r="S4" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="252"/>
-      <c r="U4" s="252"/>
-      <c r="V4" s="252"/>
-      <c r="W4" s="252"/>
-      <c r="X4" s="252"/>
-      <c r="Y4" s="252"/>
-      <c r="Z4" s="252"/>
-      <c r="AA4" s="252"/>
-      <c r="AB4" s="252"/>
-      <c r="AC4" s="252"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -16606,33 +16618,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="248"/>
+      <c r="K10" s="248"/>
+      <c r="L10" s="248"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="251" t="s">
+      <c r="S10" s="249" t="s">
         <v>118</v>
       </c>
-      <c r="T10" s="252"/>
-      <c r="U10" s="252"/>
-      <c r="V10" s="252"/>
-      <c r="W10" s="252"/>
-      <c r="X10" s="252"/>
-      <c r="Y10" s="252"/>
-      <c r="Z10" s="252"/>
-      <c r="AA10" s="252"/>
-      <c r="AB10" s="252"/>
-      <c r="AC10" s="252"/>
+      <c r="T10" s="250"/>
+      <c r="U10" s="250"/>
+      <c r="V10" s="250"/>
+      <c r="W10" s="250"/>
+      <c r="X10" s="250"/>
+      <c r="Y10" s="250"/>
+      <c r="Z10" s="250"/>
+      <c r="AA10" s="250"/>
+      <c r="AB10" s="250"/>
+      <c r="AC10" s="250"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -17019,35 +17031,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>110</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>111</v>
       </c>
@@ -17056,31 +17068,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="248" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="P4" s="252" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="P4" s="250" t="s">
         <v>112</v>
       </c>
-      <c r="Q4" s="252"/>
-      <c r="R4" s="252"/>
-      <c r="S4" s="252"/>
-      <c r="T4" s="252"/>
-      <c r="U4" s="252"/>
-      <c r="V4" s="252"/>
-      <c r="W4" s="252"/>
-      <c r="X4" s="252"/>
-      <c r="Y4" s="252"/>
-      <c r="Z4" s="252"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17275,32 +17287,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="248" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="252" t="s">
+      <c r="P9" s="250" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="252"/>
-      <c r="R9" s="252"/>
-      <c r="S9" s="252"/>
-      <c r="T9" s="252"/>
-      <c r="U9" s="252"/>
-      <c r="V9" s="252"/>
-      <c r="W9" s="252"/>
-      <c r="X9" s="252"/>
-      <c r="Y9" s="252"/>
-      <c r="Z9" s="252"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -17966,31 +17978,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="239" t="s">
+      <c r="C19" s="248" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="239"/>
-      <c r="E19" s="239"/>
-      <c r="F19" s="239"/>
-      <c r="G19" s="239"/>
-      <c r="H19" s="239"/>
-      <c r="I19" s="239"/>
-      <c r="J19" s="239"/>
-      <c r="K19" s="239"/>
-      <c r="L19" s="239"/>
-      <c r="P19" s="252" t="s">
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="248"/>
+      <c r="H19" s="248"/>
+      <c r="I19" s="248"/>
+      <c r="J19" s="248"/>
+      <c r="K19" s="248"/>
+      <c r="L19" s="248"/>
+      <c r="P19" s="250" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="252"/>
-      <c r="R19" s="252"/>
-      <c r="S19" s="252"/>
-      <c r="T19" s="252"/>
-      <c r="U19" s="252"/>
-      <c r="V19" s="252"/>
-      <c r="W19" s="252"/>
-      <c r="X19" s="252"/>
-      <c r="Y19" s="252"/>
-      <c r="Z19" s="252"/>
+      <c r="Q19" s="250"/>
+      <c r="R19" s="250"/>
+      <c r="S19" s="250"/>
+      <c r="T19" s="250"/>
+      <c r="U19" s="250"/>
+      <c r="V19" s="250"/>
+      <c r="W19" s="250"/>
+      <c r="X19" s="250"/>
+      <c r="Y19" s="250"/>
+      <c r="Z19" s="250"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="s">
@@ -18638,20 +18650,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="253"/>
       <c r="Q3" s="253"/>
       <c r="R3" s="253"/>
@@ -18669,18 +18681,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="248" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
       <c r="P5" s="253"/>
       <c r="Q5" s="253"/>
       <c r="R5" s="253"/>
@@ -18877,18 +18889,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="248" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
       <c r="P11" s="253"/>
       <c r="Q11" s="253"/>
@@ -19142,18 +19154,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="248" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19371,18 +19383,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="248" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19574,18 +19586,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="239" t="s">
+      <c r="C33" s="248" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19769,18 +19781,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="248" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20094,20 +20106,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="S2" s="253"/>
       <c r="T2" s="253"/>
       <c r="U2" s="253"/>
@@ -20125,18 +20137,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="S4" s="253"/>
       <c r="T4" s="253"/>
       <c r="U4" s="253"/>
@@ -20510,18 +20522,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="248" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20614,18 +20626,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="248" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20817,18 +20829,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="248" t="s">
         <v>255</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20966,18 +20978,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="248" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21188,10 +21200,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="242" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21208,7 +21220,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21217,7 +21229,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>99539.04</v>
+        <v>97617.26999999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21235,7 +21247,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21244,7 +21256,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0379999999999998</v>
+        <v>2.0444</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21276,10 +21288,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="242" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21287,7 +21299,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.8688793337642508E-2</v>
+        <v>2.9237070576796687E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21296,7 +21308,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97131120666235748</v>
+        <v>0.9707629294232033</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21314,7 +21326,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14354999999999998</v>
+        <v>0.14454800000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21323,7 +21335,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14072358008037544</v>
+        <v>0.14163838521033836</v>
       </c>
     </row>
   </sheetData>
@@ -21368,20 +21380,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="253"/>
       <c r="Q3" s="253"/>
       <c r="R3" s="253"/>
@@ -21399,18 +21411,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
       <c r="P5" s="253"/>
       <c r="Q5" s="253"/>
       <c r="R5" s="253"/>
@@ -21667,10 +21679,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="242" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21690,10 +21702,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="242" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21807,37 +21819,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="248" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22057,18 +22069,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22262,18 +22274,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="248" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22407,18 +22419,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="239" t="s">
+      <c r="C22" s="248" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="239"/>
-      <c r="E22" s="239"/>
-      <c r="F22" s="239"/>
-      <c r="G22" s="239"/>
-      <c r="H22" s="239"/>
-      <c r="I22" s="239"/>
-      <c r="J22" s="239"/>
-      <c r="K22" s="239"/>
-      <c r="L22" s="239"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22502,18 +22514,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="239" t="s">
+      <c r="C27" s="248" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="239"/>
-      <c r="E27" s="239"/>
-      <c r="F27" s="239"/>
-      <c r="G27" s="239"/>
-      <c r="H27" s="239"/>
-      <c r="I27" s="239"/>
-      <c r="J27" s="239"/>
-      <c r="K27" s="239"/>
-      <c r="L27" s="239"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22754,7 +22766,7 @@
         <v>58.08487793028057</v>
       </c>
       <c r="D35" s="144">
-        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
         <v>-52.155553154543689</v>
       </c>
       <c r="E35" s="144">
@@ -22814,10 +22826,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="240" t="s">
+      <c r="B39" s="242" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="240"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22919,10 +22931,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="240" t="s">
+      <c r="B52" s="242" t="s">
         <v>206</v>
       </c>
-      <c r="C52" s="240"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22978,10 +22990,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="240" t="s">
+      <c r="B60" s="242" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="240"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23082,10 +23094,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="240" t="s">
+      <c r="B73" s="242" t="s">
         <v>401</v>
       </c>
-      <c r="C73" s="240"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23192,12 +23204,12 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23235,10 +23247,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="242" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23301,7 +23313,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23310,7 +23322,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.18580947859323493</v>
+        <v>0.20915425233743129</v>
       </c>
     </row>
   </sheetData>
@@ -23366,37 +23378,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="248" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23509,18 +23521,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23641,18 +23653,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="239" t="s">
+      <c r="C14" s="248" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239"/>
-      <c r="F14" s="239"/>
-      <c r="G14" s="239"/>
-      <c r="H14" s="239"/>
-      <c r="I14" s="239"/>
-      <c r="J14" s="239"/>
-      <c r="K14" s="239"/>
-      <c r="L14" s="239"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="248"/>
+      <c r="I14" s="248"/>
+      <c r="J14" s="248"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23742,10 +23754,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="242" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23846,20 +23858,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="253"/>
       <c r="Q3" s="253"/>
       <c r="R3" s="253"/>
@@ -23877,18 +23889,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
       <c r="P5" s="253"/>
       <c r="Q5" s="253"/>
       <c r="R5" s="253"/>
@@ -24139,7 +24151,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24205,7 +24217,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>97512.8</v>
+        <v>95630.15</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24232,7 +24244,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>97341.8</v>
+        <v>95459.15</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -30866,7 +30878,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30937,7 +30949,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32047,7 +32059,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>57.303167420814482</v>
+        <v>56.196832579185518</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32084,7 +32096,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.6485853658536591</v>
+        <v>8.4816097560975603</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32145,7 +32157,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>20.494493484657418</v>
+        <v>20.098812526271541</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32206,7 +32218,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>99539.04</v>
+        <v>97617.26999999999</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32267,7 +32279,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>99368.04</v>
+        <v>97446.26999999999</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32304,7 +32316,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.6557526132404181</v>
+        <v>8.4883510452961666</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32341,7 +32353,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>45.7706310456011</v>
+        <v>44.885430677107315</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32476,7 +32488,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>34.347494824016557</v>
+        <v>33.684358178053827</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32513,7 +32525,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>25.153189957588179</v>
+        <v>24.666729261927941</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32550,7 +32562,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>2.9114204838624123E-2</v>
+        <v>2.9687369868057163E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32587,7 +32599,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7451042324699937E-2</v>
+        <v>1.7794597206006683E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32636,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>8.883449147188882E-4</v>
+        <v>9.0583356817907333E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32698,7 +32710,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>8.6398261425868689E-4</v>
+        <v>8.8099165239921182E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33201,7 +33213,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7179189190492496E-3</v>
+        <v>1.7517392158170374E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34695,15 +34707,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="242" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34711,7 +34723,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34727,7 +34739,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99539.04</v>
+        <v>97617.26999999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34747,7 +34759,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99368.04</v>
+        <v>97446.26999999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34767,7 +34779,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.303167420814482</v>
+        <v>56.196832579185518</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34787,7 +34799,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6485853658536591</v>
+        <v>8.4816097560975603</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34807,7 +34819,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.494493484657418</v>
+        <v>20.098812526271541</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34827,7 +34839,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.6557526132404181</v>
+        <v>8.4883510452961666</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34836,18 +34848,18 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.7706310456011</v>
+        <v>44.885430677107315</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="242" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>239</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34898,14 +34910,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="242" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>242</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34974,14 +34986,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="242" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>249</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35057,14 +35069,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="242" t="s">
         <v>261</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35072,7 +35084,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7451042324699937E-2</v>
+        <v>1.7794597206006683E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35088,7 +35100,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>2.9114204838624123E-2</v>
+        <v>2.9687369868057163E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35104,7 +35116,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.883449147188882E-4</v>
+        <v>9.0583356817907333E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35129,18 +35141,18 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6398261425868689E-4</v>
+        <v>8.8099165239921182E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>278</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35173,18 +35185,18 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7179189190492496E-3</v>
+        <v>1.7517392158170374E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="242" t="s">
         <v>275</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>296</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35352,7 +35364,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>253.28</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35381,7 +35393,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99539.04</v>
+        <v>97617.26999999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35410,7 +35422,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99368.04</v>
+        <v>97446.26999999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35439,7 +35451,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.303167420814482</v>
+        <v>56.196832579185518</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35468,7 +35480,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6485853658536591</v>
+        <v>8.4816097560975603</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35497,7 +35509,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.494493484657418</v>
+        <v>20.098812526271541</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35526,7 +35538,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.6557526132404181</v>
+        <v>8.4883510452961666</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35555,7 +35567,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.7706310456011</v>
+        <v>44.885430677107315</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36340,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7451042324699937E-2</v>
+        <v>1.7794597206006683E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36357,7 +36369,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>2.9114204838624123E-2</v>
+        <v>2.9687369868057163E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36386,7 +36398,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.883449147188882E-4</v>
+        <v>9.0583356817907333E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36444,7 +36456,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6398261425868689E-4</v>
+        <v>8.8099165239921182E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36680,7 +36692,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7179189190492496E-3</v>
+        <v>1.7517392158170374E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37232,14 +37244,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37306,19 +37318,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="F7" s="249">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="250"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37345,19 +37357,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="F9" s="249">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="250"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37384,19 +37396,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="249">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="F11" s="249">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="250"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37423,19 +37435,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="249">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="F13" s="249">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="250"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37462,19 +37474,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="250"/>
-      <c r="F15" s="249">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="250"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37501,19 +37513,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="249">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="F17" s="249">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="250"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37540,22 +37552,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="F19" s="249">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="250"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37582,22 +37594,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="F21" s="249">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="250"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37646,22 +37658,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="249">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="250"/>
-      <c r="F25" s="249">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="250"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37689,22 +37701,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="249">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="250"/>
-      <c r="F27" s="249">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="250"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37732,22 +37744,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="249">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="250"/>
-      <c r="F29" s="249">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="250"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -37775,22 +37787,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="249">
+      <c r="C32" s="246">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="250"/>
-      <c r="F32" s="249">
+      <c r="D32" s="247"/>
+      <c r="F32" s="246">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="250"/>
+      <c r="G32" s="247"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -37818,22 +37830,22 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="249">
+      <c r="C34" s="246">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="250"/>
-      <c r="F34" s="249">
+      <c r="D34" s="247"/>
+      <c r="F34" s="246">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="250"/>
+      <c r="G34" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C301D19E-936F-0C47-8BE3-534F6BD4B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492173E-09A9-594B-80BA-85BBCF743181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2309,6 +2309,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2316,12 +2322,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2342,14 +2342,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14692,12 +14692,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
-    <v>141.4</v>
-    <v>2.0444</v>
-    <v>4.3499999999999996</v>
-    <v>1.7825000000000001E-2</v>
-    <v>0.76</v>
-    <v>3.0599999999999998E-3</v>
+    <v>147.82</v>
+    <v>2.1032999999999999</v>
+    <v>1.6</v>
+    <v>6.3449999999999999E-3</v>
+    <v>0.84</v>
+    <v>3.3119999999999998E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14705,25 +14705,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>254.13</v>
+    <v>258.10000000000002</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46294.962513402344</v>
+    <v>46300.894042800785</v>
     <v>0</v>
-    <v>246.84</v>
-    <v>95627218998</v>
+    <v>250.06</v>
+    <v>97702305396</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>251.38</v>
-    <v>56.210799999999999</v>
-    <v>244.04</v>
-    <v>248.39</v>
-    <v>249.1</v>
+    <v>254.34</v>
+    <v>57.430599999999998</v>
+    <v>252.18</v>
+    <v>253.78</v>
+    <v>254.46</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>3293269</v>
-    <v>5123818</v>
+    <v>4339258</v>
+    <v>5037778</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14745,19 +14745,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.13</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
-    <v>52.55</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>97617.26999999999</v>
+        <v>99735.54</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>97446.26999999999</v>
+        <v>99564.54</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15643,14 +15643,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>249.1</v>
+        <v>254.46</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>56.196832579185518</v>
+        <v>57.41628959276018</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15667,14 +15667,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.3499999999999996</v>
+        <v>1.6</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.4816097560975603</v>
+        <v>8.6656585365853669</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15691,14 +15691,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2.9687369868057163E-2</v>
+        <v>2.905684372892552E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15715,14 +15715,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.7825000000000001E-2</v>
+        <v>6.3449999999999999E-3</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.7794597206006683E-2</v>
+        <v>1.7416660099298605E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.20915425233743129</v>
+        <v>0.18347318440418686</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.0599999999999998E-3</v>
+        <v>3.3119999999999998E-3</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>9.0583356817907333E-4</v>
+        <v>8.8659468831271183E-4</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="C12" s="203" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>141.4</v>
+        <v>147.82</v>
       </c>
       <c r="E12" s="179" t="s">
         <v>98</v>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0444</v>
+        <v>2.1032999999999999</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5123818</v>
+        <v>5037778</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15833,7 +15833,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7517392158170374E-3</v>
+        <v>1.7145342572968474E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20056,6 +20056,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20063,12 +20069,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21128,16 +21128,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>97617.26999999999</v>
+        <v>99735.54</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0444</v>
+        <v>2.1032999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.9237070576796687E-2</v>
+        <v>2.8633888850255865E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9707629294232033</v>
+        <v>0.97136611114974414</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14454800000000001</v>
+        <v>0.14741850000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14163838521033836</v>
+        <v>0.14448671907145558</v>
       </c>
     </row>
   </sheetData>
@@ -23199,17 +23199,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23322,7 +23322,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.20915425233743129</v>
+        <v>0.18347318440418686</v>
       </c>
     </row>
   </sheetData>
@@ -24140,10 +24140,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="255" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="255"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="150" t="s">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24170,20 +24170,20 @@
       <c r="C17" s="153">
         <v>0.44500000000000001</v>
       </c>
-      <c r="E17" s="256" t="s">
+      <c r="E17" s="254" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="255" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="255"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="154" t="s">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>95630.15</v>
+        <v>97705.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24244,15 +24244,15 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>95459.15</v>
+        <v>97534.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="255" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="255"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="154" t="s">
@@ -24328,16 +24328,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30878,7 +30878,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32059,7 +32059,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>56.196832579185518</v>
+        <v>57.41628959276018</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32096,7 +32096,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.4816097560975603</v>
+        <v>8.6656585365853669</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>20.098812526271541</v>
+        <v>20.534951660361497</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32218,7 +32218,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>97617.26999999999</v>
+        <v>99735.54</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32279,7 +32279,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>97446.26999999999</v>
+        <v>99564.54</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32316,7 +32316,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.4883510452961666</v>
+        <v>8.672869337979094</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32353,7 +32353,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>44.885430677107315</v>
+        <v>45.861142330723169</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32450,8 +32450,8 @@
       <c r="Z152" s="49"/>
       <c r="AA152" s="49"/>
       <c r="AC152" s="64">
-        <f>AC107+AC52+AC108+AC54+AC56+AC57</f>
-        <v>3950.5144344533837</v>
+        <f>AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
+        <v>2874.5144344533837</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32488,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>33.684358178053827</v>
+        <v>34.415300207039337</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32525,7 +32525,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>24.666729261927941</v>
+        <v>34.636994271671881</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32562,7 +32562,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>2.9687369868057163E-2</v>
+        <v>2.905684372892552E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32599,7 +32599,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7794597206006683E-2</v>
+        <v>1.7416660099298605E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32636,7 +32636,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>9.0583356817907333E-4</v>
+        <v>8.8659468831271183E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32710,7 +32710,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>8.8099165239921182E-4</v>
+        <v>8.6228038671069514E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32747,7 +32747,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="149">
         <f>AC152/AC5</f>
-        <v>0.34412146641579999</v>
+        <v>0.25039324341928432</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33213,7 +33213,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7517392158170374E-3</v>
+        <v>1.7145342572968474E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34723,7 +34723,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34739,7 +34739,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>97617.26999999999</v>
+        <v>99735.54</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34759,7 +34759,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>97446.26999999999</v>
+        <v>99564.54</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34779,7 +34779,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>56.196832579185518</v>
+        <v>57.41628959276018</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34799,7 +34799,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.4816097560975603</v>
+        <v>8.6656585365853669</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34819,7 +34819,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.098812526271541</v>
+        <v>20.534951660361497</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34839,7 +34839,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.4883510452961666</v>
+        <v>8.672869337979094</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34848,7 +34848,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>44.885430677107315</v>
+        <v>45.861142330723169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7794597206006683E-2</v>
+        <v>1.7416660099298605E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35100,7 +35100,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>2.9687369868057163E-2</v>
+        <v>2.905684372892552E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35116,7 +35116,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.0583356817907333E-4</v>
+        <v>8.8659468831271183E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35141,7 +35141,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.8099165239921182E-4</v>
+        <v>8.6228038671069514E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35185,7 +35185,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7517392158170374E-3</v>
+        <v>1.7145342572968474E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>248.39</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35393,7 +35393,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>97617.26999999999</v>
+        <v>99735.54</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35422,7 +35422,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>97446.26999999999</v>
+        <v>99564.54</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35451,7 +35451,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>56.196832579185518</v>
+        <v>57.41628959276018</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35480,7 +35480,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.4816097560975603</v>
+        <v>8.6656585365853669</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.098812526271541</v>
+        <v>20.534951660361497</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35538,7 +35538,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.4883510452961666</v>
+        <v>8.672869337979094</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>44.885430677107315</v>
+        <v>45.861142330723169</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36340,7 +36340,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7794597206006683E-2</v>
+        <v>1.7416660099298605E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>2.9687369868057163E-2</v>
+        <v>2.905684372892552E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36398,7 +36398,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.0583356817907333E-4</v>
+        <v>8.8659468831271183E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36456,7 +36456,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.8099165239921182E-4</v>
+        <v>8.6228038671069514E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36692,7 +36692,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7517392158170374E-3</v>
+        <v>1.7145342572968474E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37244,14 +37244,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="246"/>
+      <c r="F3" s="247" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="246"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37318,19 +37318,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="243">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="244"/>
+      <c r="F7" s="243">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="244"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37357,19 +37357,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="243">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="244"/>
+      <c r="F9" s="243">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="244"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37396,19 +37396,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="243">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="244"/>
+      <c r="F11" s="243">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="244"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37435,19 +37435,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="243">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="244"/>
+      <c r="F13" s="243">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="244"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37474,19 +37474,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="243">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="244"/>
+      <c r="F15" s="243">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37513,19 +37513,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="243">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="244"/>
+      <c r="F17" s="243">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="244"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37552,22 +37552,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="243">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="244"/>
+      <c r="F19" s="243">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="244"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37594,22 +37594,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="243">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="244"/>
+      <c r="F21" s="243">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="244"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37658,22 +37658,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="243">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="244"/>
+      <c r="F25" s="243">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="244"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37701,22 +37701,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="243">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="244"/>
+      <c r="F27" s="243">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="244"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37744,22 +37744,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="243">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="244"/>
+      <c r="F29" s="243">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="244"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -37787,22 +37787,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="246">
+      <c r="C32" s="243">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="247"/>
-      <c r="F32" s="246">
+      <c r="D32" s="244"/>
+      <c r="F32" s="243">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="247"/>
+      <c r="G32" s="244"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -37830,25 +37830,43 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="246">
+      <c r="C34" s="243">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="247"/>
-      <c r="F34" s="246">
+      <c r="D34" s="244"/>
+      <c r="F34" s="243">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="247"/>
+      <c r="G34" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -37859,24 +37877,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492173E-09A9-594B-80BA-85BBCF743181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6830A88-6423-9F4C-9152-B8E7C498A09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="408">
   <si>
     <t>Ticker</t>
   </si>
@@ -1370,6 +1370,12 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +1985,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2351,6 +2357,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14693,11 +14701,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.1032999999999999</v>
-    <v>1.6</v>
-    <v>6.3449999999999999E-3</v>
-    <v>0.84</v>
-    <v>3.3119999999999998E-3</v>
+    <v>2.0964</v>
+    <v>-0.95</v>
+    <v>-3.898E-3</v>
+    <v>0.08</v>
+    <v>3.2949999999999999E-4</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14705,25 +14713,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>258.10000000000002</v>
+    <v>248.49</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46300.894042800785</v>
+    <v>46304.999922164061</v>
     <v>0</v>
-    <v>250.06</v>
-    <v>97702305396</v>
+    <v>239.89</v>
+    <v>93467435196</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>254.34</v>
-    <v>57.430599999999998</v>
-    <v>252.18</v>
-    <v>253.78</v>
-    <v>254.46</v>
+    <v>246.47</v>
+    <v>55.156399999999998</v>
+    <v>243.73</v>
+    <v>242.78</v>
+    <v>242.86</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>4339258</v>
-    <v>5037778</v>
+    <v>3425996</v>
+    <v>5226844</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14745,19 +14753,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -14979,9 +14987,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15578,7 +15586,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>99735.54</v>
+        <v>95412.54</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15602,7 +15610,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>99564.54</v>
+        <v>95241.54</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15610,7 +15618,7 @@
       </c>
       <c r="I4" s="205">
         <f>'AVG target price'!C6</f>
-        <v>409.2368724529826</v>
+        <v>346.07885804065</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -15619,7 +15627,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15643,14 +15651,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>254.46</v>
+        <v>242.86</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>57.41628959276018</v>
+        <v>54.927601809954751</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15658,7 +15666,7 @@
       </c>
       <c r="I6" s="205">
         <f>'AVG target price'!C8</f>
-        <v>416.76347609499282</v>
+        <v>337.19515754169737</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -15667,14 +15675,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.6</v>
+        <v>-0.95</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.6656585365853669</v>
+        <v>8.2900487804878047</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15691,14 +15699,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.84</v>
+        <v>0.08</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2.905684372892552E-2</v>
+        <v>3.0373366016668252E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15706,7 +15714,7 @@
       </c>
       <c r="I8" s="206">
         <f>'AVG target price'!C10</f>
-        <v>300.34182473809454</v>
+        <v>271.79655814496891</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -15715,14 +15723,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.3449999999999999E-3</v>
+        <v>-3.898E-3</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.7416660099298605E-2</v>
+        <v>1.8205783013427793E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15730,7 +15738,7 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.18347318440418686</v>
+        <v>0.11951790981534274</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -15739,7 +15747,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.3119999999999998E-3</v>
+        <v>3.2949999999999999E-4</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15762,7 +15770,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>8.8659468831271183E-4</v>
+        <v>9.2676497240299857E-4</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15794,7 +15802,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1032999999999999</v>
+        <v>2.0964</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15817,7 +15825,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5037778</v>
+        <v>5226844</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15833,7 +15841,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7145342572968474E-3</v>
+        <v>1.7922172494307354E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -15844,6 +15852,10 @@
         <f>Statement!AC169</f>
         <v>0.44415584415584414</v>
       </c>
+      <c r="H16" s="239" t="s">
+        <v>407</v>
+      </c>
+      <c r="I16" s="240"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="241" t="s">
@@ -15857,6 +15869,13 @@
         <f>Statement!AC165</f>
         <v>2.5445292620865138E-2</v>
       </c>
+      <c r="H17" s="179" t="s">
+        <v>161</v>
+      </c>
+      <c r="I17" s="257">
+        <f>DCF!C15</f>
+        <v>0.115</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="178" t="s">
@@ -15872,7 +15891,13 @@
         <f>Statement!AC138</f>
         <v>121.79481880602383</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="180" t="s">
+        <v>406</v>
+      </c>
+      <c r="I18" s="258">
+        <f>Multiples!C54</f>
+        <v>0.12</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="178" t="s">
@@ -15943,7 +15968,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -15958,7 +15983,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16086,13 +16111,14 @@
       <c r="H59" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -21220,7 +21246,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21229,7 +21255,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>99735.54</v>
+        <v>95412.54</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21247,7 +21273,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21256,7 +21282,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1032999999999999</v>
+        <v>2.0964</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21299,7 +21325,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.8633888850255865E-2</v>
+        <v>2.9892466427404927E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21308,7 +21334,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97136611114974414</v>
+        <v>0.97010753357259505</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21326,7 +21352,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14741850000000001</v>
+        <v>0.14677800000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21335,7 +21361,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14448671907145558</v>
+        <v>0.14373650132594443</v>
       </c>
     </row>
   </sheetData>
@@ -22855,7 +22881,7 @@
         <v>203</v>
       </c>
       <c r="C42" s="105">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -22864,7 +22890,7 @@
       </c>
       <c r="C43" s="24">
         <f>(C40*C42)</f>
-        <v>256653.15402692161</v>
+        <v>213877.62835576801</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -22873,7 +22899,7 @@
       </c>
       <c r="C44" s="24">
         <f>C43/(1+C41)^5</f>
-        <v>148926.59798428035</v>
+        <v>124105.49832023363</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22882,7 +22908,7 @@
       </c>
       <c r="C45" s="108">
         <f>SUM(H9:K9)+C44</f>
-        <v>160659.09087402216</v>
+        <v>135837.99120997544</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22909,7 +22935,7 @@
       </c>
       <c r="C48" s="94">
         <f>C45+C46-C47</f>
-        <v>160830.09087402216</v>
+        <v>136008.99120997544</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22927,7 +22953,7 @@
       </c>
       <c r="C50" s="238">
         <f>C48/C49</f>
-        <v>409.2368724529826</v>
+        <v>346.07885804065</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23018,7 +23044,7 @@
         <v>338</v>
       </c>
       <c r="C63" s="105">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
@@ -23027,7 +23053,7 @@
       </c>
       <c r="C64" s="24">
         <f>(C61*C63)</f>
-        <v>261750.75613333835</v>
+        <v>207860.89457647456</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -23036,7 +23062,7 @@
       </c>
       <c r="C65" s="24">
         <f>C64/(1+C62)^5</f>
-        <v>151884.55321559036</v>
+        <v>120614.20402414528</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23045,7 +23071,7 @@
       </c>
       <c r="C66" s="108">
         <f>SUM(H9:K9)+C65</f>
-        <v>163617.04610533218</v>
+        <v>132346.69691388708</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23072,7 +23098,7 @@
       </c>
       <c r="C69" s="94">
         <f>C66+C67-C68</f>
-        <v>163788.04610533218</v>
+        <v>132517.69691388708</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23090,7 +23116,7 @@
       </c>
       <c r="C71" s="238">
         <f>C69/C70</f>
-        <v>416.76347609499282</v>
+        <v>337.19515754169737</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23268,7 +23294,7 @@
       </c>
       <c r="C6" s="133">
         <f>Multiples!C50</f>
-        <v>409.2368724529826</v>
+        <v>346.07885804065</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23286,7 +23312,7 @@
       </c>
       <c r="C8" s="133">
         <f>Multiples!C71</f>
-        <v>416.76347609499282</v>
+        <v>337.19515754169737</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23304,7 +23330,7 @@
       </c>
       <c r="C10" s="238">
         <f>AVERAGE(C5:C9)</f>
-        <v>300.34182473809454</v>
+        <v>271.79655814496891</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23313,7 +23339,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23322,7 +23348,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.18347318440418686</v>
+        <v>0.11951790981534274</v>
       </c>
     </row>
   </sheetData>
@@ -24151,7 +24177,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24217,7 +24243,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>97705.3</v>
+        <v>93470.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24244,7 +24270,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>97534.3</v>
+        <v>93299.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -30878,7 +30904,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30949,7 +30975,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32059,7 +32085,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>57.41628959276018</v>
+        <v>54.927601809954751</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32096,7 +32122,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.6656585365853669</v>
+        <v>8.2900487804878047</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32157,7 +32183,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>20.534951660361497</v>
+        <v>19.644871794871793</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32218,7 +32244,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>99735.54</v>
+        <v>95412.54</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32279,7 +32305,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>99564.54</v>
+        <v>95241.54</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32316,7 +32342,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.672869337979094</v>
+        <v>8.2963013937282231</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32353,7 +32379,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>45.861142330723169</v>
+        <v>43.869894058037765</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32514,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>34.415300207039337</v>
+        <v>32.923581780538299</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32525,7 +32551,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>34.636994271671881</v>
+        <v>33.133088099490124</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32562,7 +32588,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>2.905684372892552E-2</v>
+        <v>3.0373366016668252E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32599,7 +32625,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7416660099298605E-2</v>
+        <v>1.8205783013427793E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32636,7 +32662,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>8.8659468831271183E-4</v>
+        <v>9.2676497240299857E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32710,7 +32736,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>8.6228038671069514E-4</v>
+        <v>9.0134902602949265E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33213,7 +33239,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7145342572968474E-3</v>
+        <v>1.7922172494307354E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34723,7 +34749,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34739,7 +34765,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99735.54</v>
+        <v>95412.54</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34759,7 +34785,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99564.54</v>
+        <v>95241.54</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34779,7 +34805,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.41628959276018</v>
+        <v>54.927601809954751</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34799,7 +34825,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6656585365853669</v>
+        <v>8.2900487804878047</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34819,7 +34845,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.534951660361497</v>
+        <v>19.644871794871793</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34839,7 +34865,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.672869337979094</v>
+        <v>8.2963013937282231</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34848,7 +34874,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.861142330723169</v>
+        <v>43.869894058037765</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35084,7 +35110,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7416660099298605E-2</v>
+        <v>1.8205783013427793E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35100,7 +35126,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>2.905684372892552E-2</v>
+        <v>3.0373366016668252E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35116,7 +35142,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.8659468831271183E-4</v>
+        <v>9.2676497240299857E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35141,7 +35167,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6228038671069514E-4</v>
+        <v>9.0134902602949265E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35185,7 +35211,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7145342572968474E-3</v>
+        <v>1.7922172494307354E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35364,7 +35390,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>253.78</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35393,7 +35419,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>99735.54</v>
+        <v>95412.54</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35422,7 +35448,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>99564.54</v>
+        <v>95241.54</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35451,7 +35477,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>57.41628959276018</v>
+        <v>54.927601809954751</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35480,7 +35506,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.6656585365853669</v>
+        <v>8.2900487804878047</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35509,7 +35535,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>20.534951660361497</v>
+        <v>19.644871794871793</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35538,7 +35564,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.672869337979094</v>
+        <v>8.2963013937282231</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35567,7 +35593,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>45.861142330723169</v>
+        <v>43.869894058037765</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36340,7 +36366,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.7416660099298605E-2</v>
+        <v>1.8205783013427793E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36369,7 +36395,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>2.905684372892552E-2</v>
+        <v>3.0373366016668252E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36398,7 +36424,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>8.8659468831271183E-4</v>
+        <v>9.2676497240299857E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36456,7 +36482,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>8.6228038671069514E-4</v>
+        <v>9.0134902602949265E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36692,7 +36718,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7145342572968474E-3</v>
+        <v>1.7922172494307354E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6830A88-6423-9F4C-9152-B8E7C498A09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B6426B-380A-0145-96C9-4607FD415106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="414">
   <si>
     <t>Ticker</t>
   </si>
@@ -1376,6 +1376,24 @@
   </si>
   <si>
     <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1410,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1564,6 +1582,14 @@
       <sz val="12"/>
       <color rgb="FF4EA72E"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1981,11 +2007,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2303,6 +2330,14 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2315,12 +2350,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2328,6 +2357,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2348,19 +2383,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -14702,10 +14736,10 @@
     <v>379.935</v>
     <v>147.82</v>
     <v>2.0964</v>
-    <v>-0.95</v>
-    <v>-3.898E-3</v>
-    <v>0.08</v>
-    <v>3.2949999999999999E-4</v>
+    <v>-3.4</v>
+    <v>-1.4004000000000001E-2</v>
+    <v>0.44</v>
+    <v>1.838E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14713,25 +14747,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>248.49</v>
+    <v>242.82</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46304.999922164061</v>
+    <v>46307.864883946095</v>
     <v>0</v>
-    <v>239.89</v>
-    <v>93467435196</v>
+    <v>237.4</v>
+    <v>92158475316</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>246.47</v>
-    <v>55.156399999999998</v>
-    <v>243.73</v>
+    <v>239.66</v>
+    <v>54.171900000000001</v>
     <v>242.78</v>
-    <v>242.86</v>
+    <v>239.38</v>
+    <v>239.8</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>3425996</v>
-    <v>5226844</v>
+    <v>3508920</v>
+    <v>5194047</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14987,9 +15021,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15543,7 +15577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I59"/>
+  <dimension ref="B1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -15555,25 +15589,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>318</v>
       </c>
-      <c r="I2" s="240"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="244"/>
+      <c r="K2" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="179" t="s">
         <v>11</v>
       </c>
@@ -15586,7 +15625,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>95412.54</v>
+        <v>94076.34</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15596,8 +15635,11 @@
         <f>'AVG target price'!C5</f>
         <v>163.70032761345942</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="241" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="179" t="s">
         <v>0</v>
       </c>
@@ -15610,7 +15652,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>95241.54</v>
+        <v>93905.34</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15620,14 +15662,17 @@
         <f>'AVG target price'!C6</f>
         <v>346.07885804065</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="241" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="179" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15644,21 +15689,24 @@
         <f>'AVG target price'!C7</f>
         <v>238.80422150261779</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="241" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="179" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>242.86</v>
+        <v>239.8</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>54.927601809954751</v>
+        <v>54.158371040723985</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15668,21 +15716,24 @@
         <f>'AVG target price'!C8</f>
         <v>337.19515754169737</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="242" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="179" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.95</v>
+        <v>-3.4</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.2900487804878047</v>
+        <v>8.1739512195121957</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15693,20 +15744,20 @@
         <v>273.20422602641992</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="179" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.0373366016668252E-2</v>
+        <v>3.0804769828418069E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15717,20 +15768,20 @@
         <v>271.79655814496891</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="179" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.898E-3</v>
+        <v>-1.4004000000000001E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.8205783013427793E-2</v>
+        <v>1.8464366279555517E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15738,16 +15789,16 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.11951790981534274</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.13541882423330653</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="179" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.2949999999999999E-4</v>
+        <v>1.838E-3</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15757,7 +15808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="179" t="s">
         <v>7</v>
       </c>
@@ -15770,7 +15821,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>9.2676497240299857E-4</v>
+        <v>9.3992814771493027E-4</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15780,7 +15831,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="179" t="s">
         <v>8</v>
       </c>
@@ -15796,7 +15847,7 @@
         <v>0.10898685617256777</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="179" t="s">
         <v>9</v>
       </c>
@@ -15819,13 +15870,13 @@
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="180" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5226844</v>
+        <v>5194047</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15835,16 +15886,16 @@
         <v>0.38772932950804095</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="179" t="s">
         <v>283</v>
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.7922172494307354E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1.8176727538507557E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="180" t="s">
         <v>288</v>
       </c>
@@ -15852,16 +15903,16 @@
         <f>Statement!AC169</f>
         <v>0.44415584415584414</v>
       </c>
-      <c r="H16" s="239" t="s">
+      <c r="H16" s="243" t="s">
         <v>407</v>
       </c>
-      <c r="I16" s="240"/>
+      <c r="I16" s="244"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="245" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="178" t="s">
         <v>289</v>
       </c>
@@ -15872,7 +15923,7 @@
       <c r="H17" s="179" t="s">
         <v>161</v>
       </c>
-      <c r="I17" s="257">
+      <c r="I17" s="239">
         <f>DCF!C15</f>
         <v>0.115</v>
       </c>
@@ -15894,7 +15945,7 @@
       <c r="H18" s="180" t="s">
         <v>406</v>
       </c>
-      <c r="I18" s="258">
+      <c r="I18" s="240">
         <f>Multiples!C54</f>
         <v>0.12</v>
       </c>
@@ -15947,14 +15998,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="178" t="s">
@@ -16131,6 +16182,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{9A8285E3-EE3A-594B-A7E4-A6756D981DC3}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{51C95201-2E79-CB40-BE2F-DB0430E55621}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{5CC9E297-2810-F046-99BA-526EA0E694CA}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{814DC2F0-0B4A-F340-8A3F-90D55D303807}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16140,18 +16197,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>107</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2D767D2C-0293-444E-88C1-B0BF50BCE6B4}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{5B8BD37B-D046-A741-A995-03A8C14F1E03}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{720D1750-C435-3B46-A626-43D1D89EFE35}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{54771850-A26D-7747-8CD6-6DB1335E38A0}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{4577DAA1-E8D7-1C49-BCE8-9481AD6714C3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16188,36 +16284,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246" t="s">
         <v>110</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="85" t="s">
         <v>111</v>
       </c>
@@ -16228,32 +16324,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="253" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
+      <c r="AA4" s="254"/>
+      <c r="AB4" s="254"/>
+      <c r="AC4" s="254"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -16644,33 +16740,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="248" t="s">
+      <c r="C10" s="252" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="248"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="248"/>
-      <c r="K10" s="248"/>
-      <c r="L10" s="248"/>
+      <c r="D10" s="252"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="252"/>
+      <c r="L10" s="252"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="249" t="s">
+      <c r="S10" s="253" t="s">
         <v>118</v>
       </c>
-      <c r="T10" s="250"/>
-      <c r="U10" s="250"/>
-      <c r="V10" s="250"/>
-      <c r="W10" s="250"/>
-      <c r="X10" s="250"/>
-      <c r="Y10" s="250"/>
-      <c r="Z10" s="250"/>
-      <c r="AA10" s="250"/>
-      <c r="AB10" s="250"/>
-      <c r="AC10" s="250"/>
+      <c r="T10" s="254"/>
+      <c r="U10" s="254"/>
+      <c r="V10" s="254"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="254"/>
+      <c r="Y10" s="254"/>
+      <c r="Z10" s="254"/>
+      <c r="AA10" s="254"/>
+      <c r="AB10" s="254"/>
+      <c r="AC10" s="254"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -17057,35 +17153,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="P2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246" t="s">
         <v>110</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
       <c r="AB2" s="85" t="s">
         <v>111</v>
       </c>
@@ -17094,31 +17190,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="P4" s="254" t="s">
         <v>112</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="254"/>
+      <c r="R4" s="254"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17313,32 +17409,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="252"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="254" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -18004,31 +18100,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="248" t="s">
+      <c r="C19" s="252" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="248"/>
-      <c r="H19" s="248"/>
-      <c r="I19" s="248"/>
-      <c r="J19" s="248"/>
-      <c r="K19" s="248"/>
-      <c r="L19" s="248"/>
-      <c r="P19" s="250" t="s">
+      <c r="D19" s="252"/>
+      <c r="E19" s="252"/>
+      <c r="F19" s="252"/>
+      <c r="G19" s="252"/>
+      <c r="H19" s="252"/>
+      <c r="I19" s="252"/>
+      <c r="J19" s="252"/>
+      <c r="K19" s="252"/>
+      <c r="L19" s="252"/>
+      <c r="P19" s="254" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="250"/>
-      <c r="R19" s="250"/>
-      <c r="S19" s="250"/>
-      <c r="T19" s="250"/>
-      <c r="U19" s="250"/>
-      <c r="V19" s="250"/>
-      <c r="W19" s="250"/>
-      <c r="X19" s="250"/>
-      <c r="Y19" s="250"/>
-      <c r="Z19" s="250"/>
+      <c r="Q19" s="254"/>
+      <c r="R19" s="254"/>
+      <c r="S19" s="254"/>
+      <c r="T19" s="254"/>
+      <c r="U19" s="254"/>
+      <c r="V19" s="254"/>
+      <c r="W19" s="254"/>
+      <c r="X19" s="254"/>
+      <c r="Y19" s="254"/>
+      <c r="Z19" s="254"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="s">
@@ -18676,60 +18772,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18915,30 +19011,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="P11" s="257"/>
+      <c r="Q11" s="257"/>
+      <c r="R11" s="257"/>
+      <c r="S11" s="257"/>
+      <c r="T11" s="257"/>
+      <c r="U11" s="257"/>
+      <c r="V11" s="257"/>
+      <c r="W11" s="257"/>
+      <c r="X11" s="257"/>
+      <c r="Y11" s="257"/>
+      <c r="Z11" s="257"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19180,18 +19276,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="252" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="252"/>
+      <c r="J18" s="252"/>
+      <c r="K18" s="252"/>
+      <c r="L18" s="252"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19404,23 +19500,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
+      <c r="B25" s="257"/>
+      <c r="C25" s="257"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="248" t="s">
+      <c r="C26" s="252" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="D26" s="252"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="252"/>
+      <c r="K26" s="252"/>
+      <c r="L26" s="252"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19612,18 +19708,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="248"/>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
+      <c r="I33" s="252"/>
+      <c r="J33" s="252"/>
+      <c r="K33" s="252"/>
+      <c r="L33" s="252"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19807,18 +19903,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="252" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
+      <c r="D40" s="252"/>
+      <c r="E40" s="252"/>
+      <c r="F40" s="252"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+      <c r="K40" s="252"/>
+      <c r="L40" s="252"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20082,12 +20178,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20095,6 +20185,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20132,60 +20228,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="257"/>
+      <c r="V2" s="257"/>
+      <c r="W2" s="257"/>
+      <c r="X2" s="257"/>
+      <c r="Y2" s="257"/>
+      <c r="Z2" s="257"/>
+      <c r="AA2" s="257"/>
+      <c r="AB2" s="257"/>
+      <c r="AC2" s="257"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20548,18 +20644,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="248" t="s">
+      <c r="C13" s="252" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
+      <c r="D13" s="252"/>
+      <c r="E13" s="252"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="252"/>
+      <c r="H13" s="252"/>
+      <c r="I13" s="252"/>
+      <c r="J13" s="252"/>
+      <c r="K13" s="252"/>
+      <c r="L13" s="252"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20652,18 +20748,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="252" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="252"/>
+      <c r="J18" s="252"/>
+      <c r="K18" s="252"/>
+      <c r="L18" s="252"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20855,18 +20951,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="248" t="s">
+      <c r="C25" s="252" t="s">
         <v>255</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21004,18 +21100,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="248" t="s">
+      <c r="C31" s="252" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
+      <c r="D31" s="252"/>
+      <c r="E31" s="252"/>
+      <c r="F31" s="252"/>
+      <c r="G31" s="252"/>
+      <c r="H31" s="252"/>
+      <c r="I31" s="252"/>
+      <c r="J31" s="252"/>
+      <c r="K31" s="252"/>
+      <c r="L31" s="252"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21154,16 +21250,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21177,18 +21273,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>160</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{015C8B52-1C0C-DB42-8BAA-0C0382212135}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{BFD7282A-5263-9F45-9A26-534106C9377D}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{90BAE1C4-C36D-554D-9516-059B8AEC76C2}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{686F9DB5-AAAB-C241-9905-3694B99C7DA1}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{36547003-7E4B-EA47-9462-9D97554A9D6B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21226,10 +21361,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="246"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21246,7 +21381,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21390,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>95412.54</v>
+        <v>94076.34</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21314,10 +21449,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="246" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="246"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21325,7 +21460,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.9892466427404927E-2</v>
+        <v>3.0304173503143905E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21334,7 +21469,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97010753357259505</v>
+        <v>0.96969582649685615</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21361,7 +21496,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14373650132594443</v>
+        <v>0.14369461095440214</v>
       </c>
     </row>
   </sheetData>
@@ -21406,60 +21541,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21705,10 +21840,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="246" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="246"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21728,10 +21863,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="246" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="246"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21845,37 +21980,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22095,18 +22230,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="252" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22300,18 +22435,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="252" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
+      <c r="D17" s="252"/>
+      <c r="E17" s="252"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
+      <c r="J17" s="252"/>
+      <c r="K17" s="252"/>
+      <c r="L17" s="252"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22445,18 +22580,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="252" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
+      <c r="D22" s="252"/>
+      <c r="E22" s="252"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="252"/>
+      <c r="H22" s="252"/>
+      <c r="I22" s="252"/>
+      <c r="J22" s="252"/>
+      <c r="K22" s="252"/>
+      <c r="L22" s="252"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22540,18 +22675,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="252" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
+      <c r="D27" s="252"/>
+      <c r="E27" s="252"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="252"/>
+      <c r="H27" s="252"/>
+      <c r="I27" s="252"/>
+      <c r="J27" s="252"/>
+      <c r="K27" s="252"/>
+      <c r="L27" s="252"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22852,10 +22987,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="246" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="246"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22957,10 +23092,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="246" t="s">
         <v>206</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="246"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23016,10 +23151,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="246" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="246"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23120,10 +23255,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="246" t="s">
         <v>401</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="246"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23225,17 +23360,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23273,10 +23408,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="246"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23339,7 +23474,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23348,7 +23483,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.11951790981534274</v>
+        <v>0.13541882423330653</v>
       </c>
     </row>
   </sheetData>
@@ -23364,18 +23499,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{1E852F44-8DB8-F84B-B4B1-2F85B49EB2F7}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{74F55457-C2AE-6042-8E0D-AEC2CD0FCA13}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{46EDEF29-0E50-524C-A995-CE6847FAAF68}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{4B91D5F7-939C-B04B-A0A0-B76289CAE992}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{FBA75AB5-9B6C-3A48-9FBC-A1B9BEAA9266}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23404,37 +23578,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="252" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23547,18 +23721,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="252" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="252"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23679,18 +23853,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="252" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="D14" s="252"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="252"/>
+      <c r="J14" s="252"/>
+      <c r="K14" s="252"/>
+      <c r="L14" s="252"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23780,10 +23954,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="246" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="246"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23884,60 +24058,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="257"/>
+      <c r="Q3" s="257"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="257"/>
+      <c r="T3" s="257"/>
+      <c r="U3" s="257"/>
+      <c r="V3" s="257"/>
+      <c r="W3" s="257"/>
+      <c r="X3" s="257"/>
+      <c r="Y3" s="257"/>
+      <c r="Z3" s="257"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="252" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="P5" s="257"/>
+      <c r="Q5" s="257"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24166,10 +24340,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="258" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="150" t="s">
@@ -24177,7 +24351,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24196,20 +24370,20 @@
       <c r="C17" s="153">
         <v>0.44500000000000001</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="260"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="258" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="154" t="s">
@@ -24243,7 +24417,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>93470.3</v>
+        <v>92161.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24270,15 +24444,15 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>93299.3</v>
+        <v>91990.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="258" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="154" t="s">
@@ -24354,16 +24528,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30904,7 +31078,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -30975,7 +31149,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32085,7 +32259,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>54.927601809954751</v>
+        <v>54.158371040723985</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32122,7 +32296,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.2900487804878047</v>
+        <v>8.1739512195121957</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32183,7 +32357,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>19.644871794871793</v>
+        <v>19.369756200084069</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32244,7 +32418,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>95412.54</v>
+        <v>94076.34</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32305,7 +32479,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>95241.54</v>
+        <v>93905.34</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32342,7 +32516,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.2963013937282231</v>
+        <v>8.1799076655052261</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32379,7 +32553,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>43.869894058037765</v>
+        <v>43.254417319207739</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32514,7 +32688,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>32.923581780538299</v>
+        <v>32.462505175983438</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32551,7 +32725,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>33.133088099490124</v>
+        <v>32.66824437354304</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32588,7 +32762,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>3.0373366016668252E-2</v>
+        <v>3.0804769828418069E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32625,7 +32799,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.8205783013427793E-2</v>
+        <v>1.8464366279555517E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32662,7 +32836,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>9.2676497240299857E-4</v>
+        <v>9.3992814771493027E-4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32736,7 +32910,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>9.0134902602949265E-4</v>
+        <v>9.1415120953897654E-4</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33239,7 +33413,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.7922172494307354E-3</v>
+        <v>1.8176727538507557E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34698,18 +34872,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="241" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="241" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="241" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="241" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="242" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>225</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{165CA364-CE28-7B40-8DC8-495CD79B56D8}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{1E17AE2D-6F9F-FB4B-9F98-91F9ECC6D663}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{B5721EC4-EFBA-B54E-8878-7238E7102253}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{59376C6C-13F5-D143-BDF2-35EC403E4D48}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{FA2FBECD-26EC-4547-8A51-73C73AD518C7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -34733,15 +34946,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="246" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="246"/>
+      <c r="E4" s="246" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34749,7 +34962,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34765,7 +34978,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>95412.54</v>
+        <v>94076.34</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34785,7 +34998,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>95241.54</v>
+        <v>93905.34</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -34805,7 +35018,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>54.927601809954751</v>
+        <v>54.158371040723985</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -34825,7 +35038,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.2900487804878047</v>
+        <v>8.1739512195121957</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -34845,7 +35058,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>19.644871794871793</v>
+        <v>19.369756200084069</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34865,7 +35078,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.2963013937282231</v>
+        <v>8.1799076655052261</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34874,18 +35087,18 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>43.869894058037765</v>
+        <v>43.254417319207739</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="246" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="246"/>
+      <c r="E15" s="246" t="s">
         <v>239</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34936,14 +35149,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="246" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="246"/>
+      <c r="E21" s="246" t="s">
         <v>242</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="246"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35012,14 +35225,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="246" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="246"/>
+      <c r="E29" s="246" t="s">
         <v>249</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="246"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35095,14 +35308,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="246"/>
+      <c r="E37" s="246" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="246"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35110,7 +35323,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.8205783013427793E-2</v>
+        <v>1.8464366279555517E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35126,7 +35339,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.0373366016668252E-2</v>
+        <v>3.0804769828418069E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35142,7 +35355,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.2676497240299857E-4</v>
+        <v>9.3992814771493027E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35167,18 +35380,18 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>9.0134902602949265E-4</v>
+        <v>9.1415120953897654E-4</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="246" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="246"/>
+      <c r="E45" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="246"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35211,18 +35424,18 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.7922172494307354E-3</v>
+        <v>1.8176727538507557E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="246" t="s">
         <v>275</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="246"/>
+      <c r="E51" s="246" t="s">
         <v>296</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="246"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35390,7 +35603,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>242.78</v>
+        <v>239.38</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35419,7 +35632,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>95412.54</v>
+        <v>94076.34</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35448,7 +35661,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>95241.54</v>
+        <v>93905.34</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35477,7 +35690,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>54.927601809954751</v>
+        <v>54.158371040723985</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35506,7 +35719,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.2900487804878047</v>
+        <v>8.1739512195121957</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35535,7 +35748,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>19.644871794871793</v>
+        <v>19.369756200084069</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35564,7 +35777,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.2963013937282231</v>
+        <v>8.1799076655052261</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35593,7 +35806,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>43.869894058037765</v>
+        <v>43.254417319207739</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36366,7 +36579,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.8205783013427793E-2</v>
+        <v>1.8464366279555517E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36395,7 +36608,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.0373366016668252E-2</v>
+        <v>3.0804769828418069E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36424,7 +36637,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.2676497240299857E-4</v>
+        <v>9.3992814771493027E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36482,7 +36695,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>9.0134902602949265E-4</v>
+        <v>9.1415120953897654E-4</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36718,7 +36931,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.7922172494307354E-3</v>
+        <v>1.8176727538507557E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37270,14 +37483,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="F3" s="247" t="s">
+      <c r="D3" s="248"/>
+      <c r="F3" s="249" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="246"/>
+      <c r="G3" s="248"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37344,19 +37557,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="243">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="244"/>
-      <c r="F7" s="243">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="244"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37383,19 +37596,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="243">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="F9" s="243">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="244"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37422,19 +37635,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="243">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="F11" s="243">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="244"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37461,19 +37674,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="243">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="F13" s="243">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="244"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37500,19 +37713,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="243">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="244"/>
-      <c r="F15" s="243">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37539,19 +37752,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="243">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="F17" s="243">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="244"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37578,22 +37791,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="243">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="244"/>
-      <c r="F19" s="243">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="244"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37620,22 +37833,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="243">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="F21" s="243">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="244"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37684,22 +37897,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="243">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="F25" s="243">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="244"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37727,22 +37940,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="243">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="F27" s="243">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="244"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37770,22 +37983,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="243">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="244"/>
-      <c r="F29" s="243">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="244"/>
+      <c r="G29" s="251"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -37813,22 +38026,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="243">
+      <c r="C32" s="250">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="244"/>
-      <c r="F32" s="243">
+      <c r="D32" s="251"/>
+      <c r="F32" s="250">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="244"/>
+      <c r="G32" s="251"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -37856,43 +38069,25 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="243">
+      <c r="C34" s="250">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="244"/>
-      <c r="F34" s="243">
+      <c r="D34" s="251"/>
+      <c r="F34" s="250">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="244"/>
+      <c r="G34" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -37903,6 +38098,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B6426B-380A-0145-96C9-4607FD415106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D6E10C-64E3-8440-9F11-925BBA8D79C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -14735,11 +14735,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.0964</v>
-    <v>-3.4</v>
-    <v>-1.4004000000000001E-2</v>
-    <v>0.44</v>
-    <v>1.838E-3</v>
+    <v>2.1042000000000001</v>
+    <v>-8.0500000000000007</v>
+    <v>-3.6125999999999998E-2</v>
+    <v>-1E-4</v>
+    <v>-4.6570000000000005E-7</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14747,25 +14747,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>242.82</v>
+    <v>215.36</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46307.864883946095</v>
+    <v>46310.910163969529</v>
     <v>0</v>
-    <v>237.4</v>
-    <v>92158475316</v>
+    <v>204.38</v>
+    <v>82687765596</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>239.66</v>
-    <v>54.171900000000001</v>
-    <v>242.78</v>
-    <v>239.38</v>
-    <v>239.8</v>
+    <v>212.2</v>
+    <v>48.604900000000001</v>
+    <v>222.83</v>
+    <v>214.78</v>
+    <v>214.7499</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>3508920</v>
-    <v>5194047</v>
+    <v>12902945</v>
+    <v>5107252</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14789,17 +14789,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>94076.34</v>
+        <v>84408.54</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>93905.34</v>
+        <v>84237.54</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15699,14 +15699,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>239.8</v>
+        <v>214.7499</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>54.158371040723985</v>
+        <v>48.592760180995477</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15726,14 +15726,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.4</v>
+        <v>-8.0500000000000007</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>8.1739512195121957</v>
+        <v>7.333951219512195</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15750,14 +15750,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.44</v>
+        <v>-1E-4</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.0804769828418069E-2</v>
+        <v>3.4333018910171889E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15774,14 +15774,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.4004000000000001E-2</v>
+        <v>-3.6125999999999998E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>1.8464366279555517E-2</v>
+        <v>2.0579197318186051E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.13541882423330653</v>
+        <v>0.26546493223283785</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.838E-3</v>
+        <v>-4.6570000000000005E-7</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>9.3992814771493027E-4</v>
+        <v>1.0475835738895615E-3</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0964</v>
+        <v>2.1042000000000001</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I13" s="207">
         <f>'Reverse DCF'!C17</f>
-        <v>0.44500000000000001</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5194047</v>
+        <v>5107252</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>1.8176727538507557E-3</v>
+        <v>2.0258613642648009E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>94076.34</v>
+        <v>84408.54</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0964</v>
+        <v>2.1042000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>3.0304173503143905E-2</v>
+        <v>3.3658261488972802E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.96969582649685615</v>
+        <v>0.96634173851102723</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14677800000000002</v>
+        <v>0.146589</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14369461095440214</v>
+        <v>0.14317070062144144</v>
       </c>
     </row>
   </sheetData>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.13541882423330653</v>
+        <v>0.26546493223283785</v>
       </c>
     </row>
   </sheetData>
@@ -24198,23 +24198,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>2633.2794087256029</v>
+        <v>2569.4975545350171</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>3805.0887456084965</v>
+        <v>3622.991551894374</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>5498.3532374042779</v>
+        <v>5108.4180881710672</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>7945.120428049182</v>
+        <v>7202.8695043212047</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>11480.699018531068</v>
+        <v>10156.046001092898</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -24246,7 +24246,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>123266.45262001778</v>
+        <v>109043.86232752375</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24300,23 +24300,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>2361.6855683637696</v>
+        <v>2304.4821116905982</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>3060.659772453495</v>
+        <v>2914.1881412410253</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>3966.5052656460093</v>
+        <v>3685.2065283855118</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>5140.4485281242005</v>
+        <v>4660.2163273754004</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>6661.8368817394348</v>
+        <v>5893.1883601787567</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24335,7 +24335,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>71527.090730254989</v>
+        <v>63274.232919814021</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24351,7 +24351,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="C16" s="151">
         <f>C36</f>
-        <v>241.27071882229066</v>
+        <v>215.33120620437745</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24368,7 +24368,7 @@
         <v>317</v>
       </c>
       <c r="C17" s="153">
-        <v>0.44500000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="E17" s="260" t="s">
         <v>221</v>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>92161.3</v>
+        <v>82690.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>91990.3</v>
+        <v>82519.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24460,7 +24460,7 @@
       </c>
       <c r="C29" s="156">
         <f>SUM(H10:L10)</f>
-        <v>21191.136016326913</v>
+        <v>19457.281468871293</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="C30" s="156">
         <f>L11</f>
-        <v>71527.090730254989</v>
+        <v>63274.232919814021</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="C31" s="159">
         <f>C29+C30</f>
-        <v>92718.226746581902</v>
+        <v>82731.514388685318</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="C34" s="159">
         <f>C31+C32-C33</f>
-        <v>92889.226746581902</v>
+        <v>82902.514388685318</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C36" s="162">
         <f>C34/C35</f>
-        <v>241.27071882229066</v>
+        <v>215.33120620437745</v>
       </c>
     </row>
   </sheetData>
@@ -31078,7 +31078,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31149,7 +31149,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32259,7 +32259,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>54.158371040723985</v>
+        <v>48.592760180995477</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32296,7 +32296,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>8.1739512195121957</v>
+        <v>7.333951219512195</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>19.369756200084069</v>
+        <v>17.379213955443465</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32418,7 +32418,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>94076.34</v>
+        <v>84408.54</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>93905.34</v>
+        <v>84237.54</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32516,7 +32516,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>8.1799076655052261</v>
+        <v>7.337764808362369</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32553,7 +32553,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>43.254417319207739</v>
+        <v>38.801262091202211</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32688,7 +32688,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>32.462505175983438</v>
+        <v>29.126480331262936</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32725,7 +32725,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>32.66824437354304</v>
+        <v>29.304963297572922</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32762,7 +32762,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>3.0804769828418069E-2</v>
+        <v>3.4333018910171889E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32799,7 +32799,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.8464366279555517E-2</v>
+        <v>2.0579197318186051E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32836,7 +32836,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>9.3992814771493027E-4</v>
+        <v>1.0475835738895615E-3</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32910,7 +32910,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>9.1415120953897654E-4</v>
+        <v>1.0188542533729407E-3</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33413,7 +33413,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>1.8176727538507557E-3</v>
+        <v>2.0258613642648009E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34962,7 +34962,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34978,7 +34978,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>94076.34</v>
+        <v>84408.54</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>93905.34</v>
+        <v>84237.54</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -35018,7 +35018,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>54.158371040723985</v>
+        <v>48.592760180995477</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -35038,7 +35038,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.1739512195121957</v>
+        <v>7.333951219512195</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>19.369756200084069</v>
+        <v>17.379213955443465</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.1799076655052261</v>
+        <v>7.337764808362369</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>43.254417319207739</v>
+        <v>38.801262091202211</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.8464366279555517E-2</v>
+        <v>2.0579197318186051E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35339,7 +35339,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.0804769828418069E-2</v>
+        <v>3.4333018910171889E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.3992814771493027E-4</v>
+        <v>1.0475835738895615E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35380,7 +35380,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>9.1415120953897654E-4</v>
+        <v>1.0188542533729407E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35424,7 +35424,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>1.8176727538507557E-3</v>
+        <v>2.0258613642648009E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35603,7 +35603,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>239.38</v>
+        <v>214.78</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>94076.34</v>
+        <v>84408.54</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35661,7 +35661,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>93905.34</v>
+        <v>84237.54</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35690,7 +35690,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>54.158371040723985</v>
+        <v>48.592760180995477</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>8.1739512195121957</v>
+        <v>7.333951219512195</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>19.369756200084069</v>
+        <v>17.379213955443465</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +35777,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>8.1799076655052261</v>
+        <v>7.337764808362369</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>43.254417319207739</v>
+        <v>38.801262091202211</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36579,7 +36579,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>1.8464366279555517E-2</v>
+        <v>2.0579197318186051E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.0804769828418069E-2</v>
+        <v>3.4333018910171889E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>9.3992814771493027E-4</v>
+        <v>1.0475835738895615E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>9.1415120953897654E-4</v>
+        <v>1.0188542533729407E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36931,7 +36931,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>1.8176727538507557E-3</v>
+        <v>2.0258613642648009E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D6E10C-64E3-8440-9F11-925BBA8D79C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D055C24-1444-284A-AF95-6FE5EB7F8F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="415">
   <si>
     <t>Ticker</t>
   </si>
@@ -1394,6 +1424,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2012,7 +2045,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2350,6 +2383,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2357,12 +2396,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2383,15 +2416,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -14716,7 +14752,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=b19hc7&amp;q=XNYS%3aVRT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -14735,11 +14771,9 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.1042000000000001</v>
-    <v>-8.0500000000000007</v>
-    <v>-3.6125999999999998E-2</v>
-    <v>-1E-4</v>
-    <v>-4.6570000000000005E-7</v>
+    <v>2.1105999999999998</v>
+    <v>-2.6</v>
+    <v>-1.2616E-2</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14747,35 +14781,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>215.36</v>
+    <v>208.94</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46310.910163969529</v>
+    <v>46315.734017765622</v>
     <v>0</v>
-    <v>204.38</v>
-    <v>82687765596</v>
+    <v>197.9</v>
+    <v>78337398936</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>212.2</v>
-    <v>48.604900000000001</v>
-    <v>222.83</v>
-    <v>214.78</v>
-    <v>214.7499</v>
+    <v>202.35</v>
+    <v>46.047699999999999</v>
+    <v>206.08</v>
+    <v>203.48</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>12902945</v>
-    <v>5107252</v>
+    <v>4213895</v>
+    <v>5048685</v>
     <v>2016</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -14789,28 +14837,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -14832,8 +14880,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -14854,7 +14900,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -14864,6 +14909,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -14899,7 +14949,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -14910,16 +14960,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15013,19 +15060,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15097,9 +15138,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15107,9 +15145,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -15587,7 +15622,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -15625,7 +15660,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>84408.54</v>
+        <v>79967.64</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15652,7 +15687,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>84237.54</v>
+        <v>79796.639999999999</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15672,7 +15707,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15697,16 +15732,16 @@
       <c r="B6" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="202" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>214.7499</v>
+      <c r="C6" s="202" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>48.592760180995477</v>
+        <v>46.036199095022624</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15726,14 +15761,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-8.0500000000000007</v>
+        <v>-2.6</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>7.333951219512195</v>
+        <v>6.9480975609756097</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15748,16 +15783,16 @@
       <c r="B8" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1E-4</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.4333018910171889E-2</v>
+        <v>3.6239658942042056E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15774,14 +15809,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.6125999999999998E-2</v>
+        <v>-1.2616E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>2.0579197318186051E-2</v>
+        <v>2.1722036563790053E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15789,16 +15824,16 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.26546493223283785</v>
+        <v>0.33574089908083804</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.6570000000000005E-7</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15821,7 +15856,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>1.0475835738895615E-3</v>
+        <v>1.1057597798309418E-3</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15853,7 +15888,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1042000000000001</v>
+        <v>2.1105999999999998</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15862,12 +15897,12 @@
         <f>Statement!AC123</f>
         <v>0.36422866750735605</v>
       </c>
-      <c r="H13" s="178" t="s">
+      <c r="H13" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="I13" s="207">
+      <c r="I13" s="261">
         <f>'Reverse DCF'!C17</f>
-        <v>0.41</v>
+        <v>0.39500000000000002</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -15876,7 +15911,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5107252</v>
+        <v>5048685</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15885,6 +15920,13 @@
         <f>Statement!AC134</f>
         <v>0.38772932950804095</v>
       </c>
+      <c r="H14" s="180" t="s">
+        <v>414</v>
+      </c>
+      <c r="I14" s="262">
+        <f>'Reverse DCF'!C16</f>
+        <v>204.94318402936929</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="179" t="s">
@@ -15892,7 +15934,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>2.0258613642648009E-3</v>
+        <v>2.1383649686298107E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16014,12 +16056,12 @@
       <c r="C26" s="164">
         <v>0.21</v>
       </c>
-      <c r="E26" s="179" t="e" vm="2">
+      <c r="E26" s="179" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16034,7 +16076,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20178,6 +20220,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20185,12 +20233,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21250,16 +21292,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21381,7 +21423,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21390,7 +21432,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>84408.54</v>
+        <v>79967.64</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21408,7 +21450,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21417,7 +21459,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1042000000000001</v>
+        <v>2.1105999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21460,7 +21502,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>3.3658261488972802E-2</v>
+        <v>3.5461146885859975E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21469,7 +21511,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.96634173851102723</v>
+        <v>0.96453885311414</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21487,7 +21529,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.146589</v>
+        <v>0.14633699999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21496,7 +21538,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14317070062144144</v>
+        <v>0.14274453759243416</v>
       </c>
     </row>
   </sheetData>
@@ -23360,17 +23402,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23474,7 +23516,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23483,7 +23525,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.26546493223283785</v>
+        <v>0.33574089908083804</v>
       </c>
     </row>
   </sheetData>
@@ -24198,23 +24240,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>2569.4975545350171</v>
+        <v>2542.1624741676233</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>3622.991551894374</v>
+        <v>3546.3166514638347</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>5108.4180881710672</v>
+        <v>4947.1117287920497</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>7202.8695043212047</v>
+        <v>6901.2208616649095</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>10156.046001092898</v>
+        <v>9627.2031020225495</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -24246,7 +24288,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>109043.86232752375</v>
+        <v>103365.7596217158</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24300,23 +24342,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>2304.4821116905982</v>
+        <v>2279.9663445449537</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>2914.1881412410253</v>
+        <v>2852.5139467625204</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>3685.2065283855118</v>
+        <v>3568.8403190436916</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>4660.2163273754004</v>
+        <v>4465.0513408663228</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>5893.1883601787567</v>
+        <v>5586.3198390210946</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24335,15 +24377,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>63274.232919814021</v>
+        <v>59979.434061068598</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="259" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="260"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="150" t="s">
@@ -24351,7 +24393,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24360,7 +24402,7 @@
       </c>
       <c r="C16" s="151">
         <f>C36</f>
-        <v>215.33120620437745</v>
+        <v>204.94318402936929</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24368,22 +24410,22 @@
         <v>317</v>
       </c>
       <c r="C17" s="153">
-        <v>0.41</v>
-      </c>
-      <c r="E17" s="260" t="s">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E17" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="260"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="154" t="s">
@@ -24417,7 +24459,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>82690.3</v>
+        <v>78339.8</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24444,15 +24486,15 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>82519.3</v>
+        <v>78168.800000000003</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="259" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="260"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="154" t="s">
@@ -24460,7 +24502,7 @@
       </c>
       <c r="C29" s="156">
         <f>SUM(H10:L10)</f>
-        <v>19457.281468871293</v>
+        <v>18752.691790238583</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24469,7 +24511,7 @@
       </c>
       <c r="C30" s="156">
         <f>L11</f>
-        <v>63274.232919814021</v>
+        <v>59979.434061068598</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24478,7 +24520,7 @@
       </c>
       <c r="C31" s="159">
         <f>C29+C30</f>
-        <v>82731.514388685318</v>
+        <v>78732.125851307181</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24505,7 +24547,7 @@
       </c>
       <c r="C34" s="159">
         <f>C31+C32-C33</f>
-        <v>82902.514388685318</v>
+        <v>78903.125851307181</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24523,21 +24565,21 @@
       </c>
       <c r="C36" s="162">
         <f>C34/C35</f>
-        <v>215.33120620437745</v>
+        <v>204.94318402936929</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31078,7 +31120,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31149,7 +31191,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32259,7 +32301,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>48.592760180995477</v>
+        <v>46.036199095022624</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32296,7 +32338,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>7.333951219512195</v>
+        <v>6.9480975609756097</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32357,7 +32399,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>17.379213955443465</v>
+        <v>16.464859184531313</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32418,7 +32460,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>84408.54</v>
+        <v>79967.64</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32479,7 +32521,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>84237.54</v>
+        <v>79796.639999999999</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32516,7 +32558,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>7.337764808362369</v>
+        <v>6.9509268292682922</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32553,7 +32595,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>38.801262091202211</v>
+        <v>36.755707047443572</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32688,7 +32730,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>29.126480331262936</v>
+        <v>27.594078674948239</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32725,7 +32767,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>29.304963297572922</v>
+        <v>27.760041502513481</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32762,7 +32804,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>3.4333018910171889E-2</v>
+        <v>3.6239658942042056E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32799,7 +32841,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.0579197318186051E-2</v>
+        <v>2.1722036563790053E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32836,7 +32878,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>1.0475835738895615E-3</v>
+        <v>1.1057597798309418E-3</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32910,7 +32952,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>1.0188542533729407E-3</v>
+        <v>1.0754350134629458E-3</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33413,7 +33455,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>2.0258613642648009E-3</v>
+        <v>2.1383649686298107E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34962,7 +35004,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34978,7 +35020,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>84408.54</v>
+        <v>79967.64</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34998,7 +35040,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>84237.54</v>
+        <v>79796.639999999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -35018,7 +35060,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>48.592760180995477</v>
+        <v>46.036199095022624</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -35038,7 +35080,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>7.333951219512195</v>
+        <v>6.9480975609756097</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -35058,7 +35100,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>17.379213955443465</v>
+        <v>16.464859184531313</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35078,7 +35120,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>7.337764808362369</v>
+        <v>6.9509268292682922</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35087,7 +35129,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>38.801262091202211</v>
+        <v>36.755707047443572</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35323,7 +35365,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.0579197318186051E-2</v>
+        <v>2.1722036563790053E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35339,7 +35381,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.4333018910171889E-2</v>
+        <v>3.6239658942042056E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35355,7 +35397,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.0475835738895615E-3</v>
+        <v>1.1057597798309418E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35380,7 +35422,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0188542533729407E-3</v>
+        <v>1.0754350134629458E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35424,7 +35466,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>2.0258613642648009E-3</v>
+        <v>2.1383649686298107E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35603,7 +35645,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>214.78</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35632,7 +35674,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>84408.54</v>
+        <v>79967.64</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35661,7 +35703,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>84237.54</v>
+        <v>79796.639999999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35690,7 +35732,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>48.592760180995477</v>
+        <v>46.036199095022624</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35761,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>7.333951219512195</v>
+        <v>6.9480975609756097</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35790,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>17.379213955443465</v>
+        <v>16.464859184531313</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +35819,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>7.337764808362369</v>
+        <v>6.9509268292682922</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +35848,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>38.801262091202211</v>
+        <v>36.755707047443572</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36579,7 +36621,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.0579197318186051E-2</v>
+        <v>2.1722036563790053E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36608,7 +36650,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.4333018910171889E-2</v>
+        <v>3.6239658942042056E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36637,7 +36679,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.0475835738895615E-3</v>
+        <v>1.1057597798309418E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36695,7 +36737,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0188542533729407E-3</v>
+        <v>1.0754350134629458E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36931,7 +36973,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>2.0258613642648009E-3</v>
+        <v>2.1383649686298107E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37483,14 +37525,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="249" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37557,19 +37599,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="247">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37596,19 +37638,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="247">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37635,19 +37677,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="247">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37674,19 +37716,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="247">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37713,19 +37755,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="247">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37752,19 +37794,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="247">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37791,22 +37833,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37833,22 +37875,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37897,22 +37939,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37940,22 +37982,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37983,22 +38025,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -38026,22 +38068,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="250">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="F32" s="250">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="251"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -38069,25 +38111,43 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="250">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="F34" s="250">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="251"/>
+      <c r="G34" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -38098,24 +38158,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D055C24-1444-284A-AF95-6FE5EB7F8F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE1E6A0-07FE-9B4F-945A-417095AD1570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2371,6 +2341,9 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,12 +2356,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2396,6 +2363,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,18 +2389,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -14752,7 +14722,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=b19hc7&amp;q=XNYS%3aVRT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -14771,9 +14741,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.1105999999999998</v>
-    <v>-2.6</v>
-    <v>-1.2616E-2</v>
+    <v>2.1187999999999998</v>
+    <v>-1.2849999999999999</v>
+    <v>-6.5700000000000003E-3</v>
+    <v>0.19</v>
+    <v>9.7780000000000002E-4</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14781,49 +14753,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>208.94</v>
+    <v>196.73</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46315.734017765622</v>
+    <v>46318.953736689065</v>
     <v>0</v>
-    <v>197.9</v>
-    <v>78337398936</v>
+    <v>187.24</v>
+    <v>74805132201</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>202.35</v>
-    <v>46.047699999999999</v>
-    <v>206.08</v>
-    <v>203.48</v>
+    <v>191.6</v>
+    <v>43.971400000000003</v>
+    <v>195.59</v>
+    <v>194.30500000000001</v>
+    <v>194.51</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>4213895</v>
-    <v>5048685</v>
+    <v>7393446</v>
+    <v>5265947</v>
     <v>2016</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -14837,28 +14795,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -14880,6 +14838,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -14900,6 +14860,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -14909,11 +14870,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -14949,7 +14905,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -14960,13 +14916,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15060,13 +15019,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15138,6 +15103,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15145,6 +15113,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -15631,18 +15602,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="247"/>
+      <c r="E2" s="246" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="247"/>
+      <c r="H2" s="246" t="s">
         <v>318</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="247"/>
       <c r="K2" s="132" t="s">
         <v>408</v>
       </c>
@@ -15660,7 +15631,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>79967.64</v>
+        <v>76361.865000000005</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15687,7 +15658,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>79796.639999999999</v>
+        <v>76190.865000000005</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15707,7 +15678,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15732,16 +15703,16 @@
       <c r="B6" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="202" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="202" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>194.51</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>46.036199095022624</v>
+        <v>43.960407239819006</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15761,14 +15732,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.6</v>
+        <v>-1.2849999999999999</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>6.9480975609756097</v>
+        <v>6.6348048780487812</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15783,16 +15754,16 @@
       <c r="B8" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.19</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.6239658942042056E-2</v>
+        <v>3.7950880324884674E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15809,14 +15780,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.2616E-2</v>
+        <v>-6.5700000000000003E-3</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>2.1722036563790053E-2</v>
+        <v>2.2747741952085638E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15824,16 +15795,16 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.33574089908083804</v>
+        <v>0.39881401994271326</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>9.7780000000000002E-4</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15856,7 +15827,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>1.1057597798309418E-3</v>
+        <v>1.1579732894161242E-3</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15888,7 +15859,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1105999999999998</v>
+        <v>2.1187999999999998</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15897,10 +15868,10 @@
         <f>Statement!AC123</f>
         <v>0.36422866750735605</v>
       </c>
-      <c r="H13" s="263" t="s">
+      <c r="H13" s="245" t="s">
         <v>405</v>
       </c>
-      <c r="I13" s="261">
+      <c r="I13" s="243">
         <f>'Reverse DCF'!C17</f>
         <v>0.39500000000000002</v>
       </c>
@@ -15911,7 +15882,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5048685</v>
+        <v>5265947</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15923,7 +15894,7 @@
       <c r="H14" s="180" t="s">
         <v>414</v>
       </c>
-      <c r="I14" s="262">
+      <c r="I14" s="244">
         <f>'Reverse DCF'!C16</f>
         <v>204.94318402936929</v>
       </c>
@@ -15934,7 +15905,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>2.1383649686298107E-3</v>
+        <v>2.2393376589217666E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -15945,16 +15916,16 @@
         <f>Statement!AC169</f>
         <v>0.44415584415584414</v>
       </c>
-      <c r="H16" s="243" t="s">
+      <c r="H16" s="246" t="s">
         <v>407</v>
       </c>
-      <c r="I16" s="244"/>
+      <c r="I16" s="247"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="248" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="248"/>
       <c r="E17" s="178" t="s">
         <v>289</v>
       </c>
@@ -16040,14 +16011,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="248" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="248"/>
+      <c r="E25" s="246" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="247"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="178" t="s">
@@ -16056,12 +16027,12 @@
       <c r="C26" s="164">
         <v>0.21</v>
       </c>
-      <c r="E26" s="179" t="e" vm="5">
+      <c r="E26" s="179" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16076,7 +16047,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16326,36 +16297,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="246" t="s">
+      <c r="S2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>110</v>
       </c>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="85" t="s">
         <v>111</v>
       </c>
@@ -16366,32 +16337,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="253" t="s">
+      <c r="S4" s="256" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
-      <c r="AA4" s="254"/>
-      <c r="AB4" s="254"/>
-      <c r="AC4" s="254"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -16782,33 +16753,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="252" t="s">
+      <c r="C10" s="255" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="253" t="s">
+      <c r="S10" s="256" t="s">
         <v>118</v>
       </c>
-      <c r="T10" s="254"/>
-      <c r="U10" s="254"/>
-      <c r="V10" s="254"/>
-      <c r="W10" s="254"/>
-      <c r="X10" s="254"/>
-      <c r="Y10" s="254"/>
-      <c r="Z10" s="254"/>
-      <c r="AA10" s="254"/>
-      <c r="AB10" s="254"/>
-      <c r="AC10" s="254"/>
+      <c r="T10" s="257"/>
+      <c r="U10" s="257"/>
+      <c r="V10" s="257"/>
+      <c r="W10" s="257"/>
+      <c r="X10" s="257"/>
+      <c r="Y10" s="257"/>
+      <c r="Z10" s="257"/>
+      <c r="AA10" s="257"/>
+      <c r="AB10" s="257"/>
+      <c r="AC10" s="257"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -17195,35 +17166,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="P2" s="246" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>110</v>
       </c>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="85" t="s">
         <v>111</v>
       </c>
@@ -17232,31 +17203,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="P4" s="254" t="s">
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="P4" s="257" t="s">
         <v>112</v>
       </c>
-      <c r="Q4" s="254"/>
-      <c r="R4" s="254"/>
-      <c r="S4" s="254"/>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17451,32 +17422,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="255" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="254" t="s">
+      <c r="P9" s="257" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="254"/>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="254"/>
-      <c r="U9" s="254"/>
-      <c r="V9" s="254"/>
-      <c r="W9" s="254"/>
-      <c r="X9" s="254"/>
-      <c r="Y9" s="254"/>
-      <c r="Z9" s="254"/>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -18142,31 +18113,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="252" t="s">
+      <c r="C19" s="255" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="252"/>
-      <c r="E19" s="252"/>
-      <c r="F19" s="252"/>
-      <c r="G19" s="252"/>
-      <c r="H19" s="252"/>
-      <c r="I19" s="252"/>
-      <c r="J19" s="252"/>
-      <c r="K19" s="252"/>
-      <c r="L19" s="252"/>
-      <c r="P19" s="254" t="s">
+      <c r="D19" s="255"/>
+      <c r="E19" s="255"/>
+      <c r="F19" s="255"/>
+      <c r="G19" s="255"/>
+      <c r="H19" s="255"/>
+      <c r="I19" s="255"/>
+      <c r="J19" s="255"/>
+      <c r="K19" s="255"/>
+      <c r="L19" s="255"/>
+      <c r="P19" s="257" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="254"/>
-      <c r="R19" s="254"/>
-      <c r="S19" s="254"/>
-      <c r="T19" s="254"/>
-      <c r="U19" s="254"/>
-      <c r="V19" s="254"/>
-      <c r="W19" s="254"/>
-      <c r="X19" s="254"/>
-      <c r="Y19" s="254"/>
-      <c r="Z19" s="254"/>
+      <c r="Q19" s="257"/>
+      <c r="R19" s="257"/>
+      <c r="S19" s="257"/>
+      <c r="T19" s="257"/>
+      <c r="U19" s="257"/>
+      <c r="V19" s="257"/>
+      <c r="W19" s="257"/>
+      <c r="X19" s="257"/>
+      <c r="Y19" s="257"/>
+      <c r="Z19" s="257"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="s">
@@ -18814,60 +18785,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19053,30 +19024,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="257"/>
-      <c r="Q11" s="257"/>
-      <c r="R11" s="257"/>
-      <c r="S11" s="257"/>
-      <c r="T11" s="257"/>
-      <c r="U11" s="257"/>
-      <c r="V11" s="257"/>
-      <c r="W11" s="257"/>
-      <c r="X11" s="257"/>
-      <c r="Y11" s="257"/>
-      <c r="Z11" s="257"/>
+      <c r="P11" s="260"/>
+      <c r="Q11" s="260"/>
+      <c r="R11" s="260"/>
+      <c r="S11" s="260"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19318,18 +19289,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="255" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19542,23 +19513,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="257"/>
-      <c r="C25" s="257"/>
+      <c r="B25" s="260"/>
+      <c r="C25" s="260"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="252" t="s">
+      <c r="C26" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="252"/>
-      <c r="L26" s="252"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="255"/>
+      <c r="I26" s="255"/>
+      <c r="J26" s="255"/>
+      <c r="K26" s="255"/>
+      <c r="L26" s="255"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19750,18 +19721,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="252" t="s">
+      <c r="C33" s="255" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
-      <c r="I33" s="252"/>
-      <c r="J33" s="252"/>
-      <c r="K33" s="252"/>
-      <c r="L33" s="252"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19945,18 +19916,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="252" t="s">
+      <c r="C40" s="255" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="252"/>
-      <c r="E40" s="252"/>
-      <c r="F40" s="252"/>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
+      <c r="F40" s="255"/>
+      <c r="G40" s="255"/>
+      <c r="H40" s="255"/>
+      <c r="I40" s="255"/>
+      <c r="J40" s="255"/>
+      <c r="K40" s="255"/>
+      <c r="L40" s="255"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20220,12 +20191,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20233,6 +20198,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20270,60 +20241,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="S2" s="257"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="257"/>
-      <c r="V2" s="257"/>
-      <c r="W2" s="257"/>
-      <c r="X2" s="257"/>
-      <c r="Y2" s="257"/>
-      <c r="Z2" s="257"/>
-      <c r="AA2" s="257"/>
-      <c r="AB2" s="257"/>
-      <c r="AC2" s="257"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="S4" s="257"/>
-      <c r="T4" s="257"/>
-      <c r="U4" s="257"/>
-      <c r="V4" s="257"/>
-      <c r="W4" s="257"/>
-      <c r="X4" s="257"/>
-      <c r="Y4" s="257"/>
-      <c r="Z4" s="257"/>
-      <c r="AA4" s="257"/>
-      <c r="AB4" s="257"/>
-      <c r="AC4" s="257"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20686,18 +20657,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="252" t="s">
+      <c r="C13" s="255" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="252"/>
-      <c r="I13" s="252"/>
-      <c r="J13" s="252"/>
-      <c r="K13" s="252"/>
-      <c r="L13" s="252"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="255"/>
+      <c r="I13" s="255"/>
+      <c r="J13" s="255"/>
+      <c r="K13" s="255"/>
+      <c r="L13" s="255"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20790,18 +20761,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="255" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20993,18 +20964,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="255" t="s">
         <v>255</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
-      <c r="H25" s="252"/>
-      <c r="I25" s="252"/>
-      <c r="J25" s="252"/>
-      <c r="K25" s="252"/>
-      <c r="L25" s="252"/>
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
+      <c r="F25" s="255"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="255"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="255"/>
+      <c r="K25" s="255"/>
+      <c r="L25" s="255"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21142,18 +21113,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="252" t="s">
+      <c r="C31" s="255" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="252"/>
-      <c r="E31" s="252"/>
-      <c r="F31" s="252"/>
-      <c r="G31" s="252"/>
-      <c r="H31" s="252"/>
-      <c r="I31" s="252"/>
-      <c r="J31" s="252"/>
-      <c r="K31" s="252"/>
-      <c r="L31" s="252"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="K31" s="255"/>
+      <c r="L31" s="255"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21292,16 +21263,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21403,10 +21374,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21423,7 +21394,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21432,7 +21403,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>79967.64</v>
+        <v>76361.865000000005</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21450,7 +21421,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21459,7 +21430,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1105999999999998</v>
+        <v>2.1187999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21491,10 +21462,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="249" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="246"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21502,7 +21473,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>3.5461146885859975E-2</v>
+        <v>3.7073529103004071E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21511,7 +21482,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.96453885311414</v>
+        <v>0.9629264708969959</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21529,7 +21500,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14633699999999999</v>
+        <v>0.144876</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21538,7 +21509,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14274453759243416</v>
+        <v>0.14117435641318146</v>
       </c>
     </row>
   </sheetData>
@@ -21583,60 +21554,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21882,10 +21853,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="246" t="s">
+      <c r="B13" s="249" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="246"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21905,10 +21876,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="246" t="s">
+      <c r="B18" s="249" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="246"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22022,37 +21993,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22272,18 +22243,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="255" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22477,18 +22448,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="255" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
-      <c r="J17" s="252"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="252"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22622,18 +22593,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="252" t="s">
+      <c r="C22" s="255" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
-      <c r="K22" s="252"/>
-      <c r="L22" s="252"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="255"/>
+      <c r="J22" s="255"/>
+      <c r="K22" s="255"/>
+      <c r="L22" s="255"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22717,18 +22688,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="252" t="s">
+      <c r="C27" s="255" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="252"/>
-      <c r="E27" s="252"/>
-      <c r="F27" s="252"/>
-      <c r="G27" s="252"/>
-      <c r="H27" s="252"/>
-      <c r="I27" s="252"/>
-      <c r="J27" s="252"/>
-      <c r="K27" s="252"/>
-      <c r="L27" s="252"/>
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="255"/>
+      <c r="K27" s="255"/>
+      <c r="L27" s="255"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23029,10 +23000,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="246" t="s">
+      <c r="B39" s="249" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="246"/>
+      <c r="C39" s="249"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23134,10 +23105,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="246" t="s">
+      <c r="B52" s="249" t="s">
         <v>206</v>
       </c>
-      <c r="C52" s="246"/>
+      <c r="C52" s="249"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23193,10 +23164,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="246" t="s">
+      <c r="B60" s="249" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="246"/>
+      <c r="C60" s="249"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23297,10 +23268,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="246" t="s">
+      <c r="B73" s="249" t="s">
         <v>401</v>
       </c>
-      <c r="C73" s="246"/>
+      <c r="C73" s="249"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23402,17 +23373,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23450,10 +23421,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23516,7 +23487,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23525,7 +23496,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.33574089908083804</v>
+        <v>0.39881401994271326</v>
       </c>
     </row>
   </sheetData>
@@ -23620,37 +23591,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="255" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23763,18 +23734,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="255" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23895,18 +23866,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="252" t="s">
+      <c r="C14" s="255" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="252"/>
-      <c r="E14" s="252"/>
-      <c r="F14" s="252"/>
-      <c r="G14" s="252"/>
-      <c r="H14" s="252"/>
-      <c r="I14" s="252"/>
-      <c r="J14" s="252"/>
-      <c r="K14" s="252"/>
-      <c r="L14" s="252"/>
+      <c r="D14" s="255"/>
+      <c r="E14" s="255"/>
+      <c r="F14" s="255"/>
+      <c r="G14" s="255"/>
+      <c r="H14" s="255"/>
+      <c r="I14" s="255"/>
+      <c r="J14" s="255"/>
+      <c r="K14" s="255"/>
+      <c r="L14" s="255"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23996,10 +23967,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="246" t="s">
+      <c r="B20" s="249" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="246"/>
+      <c r="C20" s="249"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24100,60 +24071,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="255" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24382,10 +24353,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="259" t="s">
+      <c r="B14" s="261" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="260"/>
+      <c r="C14" s="262"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="150" t="s">
@@ -24393,7 +24364,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24412,20 +24383,20 @@
       <c r="C17" s="153">
         <v>0.39500000000000002</v>
       </c>
-      <c r="E17" s="258" t="s">
+      <c r="E17" s="263" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="259" t="s">
+      <c r="B19" s="261" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="260"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="154" t="s">
@@ -24459,7 +24430,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>78339.8</v>
+        <v>74807.425000000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24486,15 +24457,15 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>78168.800000000003</v>
+        <v>74636.425000000003</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="259" t="s">
+      <c r="B28" s="261" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="260"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="154" t="s">
@@ -24570,16 +24541,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31120,7 +31091,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31191,7 +31162,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32301,7 +32272,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>46.036199095022624</v>
+        <v>43.960407239819006</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32338,7 +32309,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>6.9480975609756097</v>
+        <v>6.6348048780487812</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32399,7 +32370,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>16.464859184531313</v>
+        <v>15.722451660361497</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32460,7 +32431,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>79967.64</v>
+        <v>76361.865000000005</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32521,7 +32492,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>79796.639999999999</v>
+        <v>76190.865000000005</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32558,7 +32529,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>6.9509268292682922</v>
+        <v>6.6368349303135892</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32595,7 +32566,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>36.755707047443572</v>
+        <v>35.094824965453711</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32730,7 +32701,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>27.594078674948239</v>
+        <v>26.349849896480332</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32767,7 +32738,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>27.760041502513481</v>
+        <v>26.50564703617097</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32804,7 +32775,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>3.6239658942042056E-2</v>
+        <v>3.7950880324884674E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32841,7 +32812,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.1722036563790053E-2</v>
+        <v>2.2747741952085638E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32878,7 +32849,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>1.1057597798309418E-3</v>
+        <v>1.1579732894161242E-3</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32952,7 +32923,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>1.0754350134629458E-3</v>
+        <v>1.1262166003934032E-3</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33455,7 +33426,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>2.1383649686298107E-3</v>
+        <v>2.2393376589217666E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34988,15 +34959,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="249" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="E4" s="246" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35004,7 +34975,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35020,7 +34991,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>79967.64</v>
+        <v>76361.865000000005</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35040,7 +35011,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>79796.639999999999</v>
+        <v>76190.865000000005</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -35060,7 +35031,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>46.036199095022624</v>
+        <v>43.960407239819006</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -35080,7 +35051,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>6.9480975609756097</v>
+        <v>6.6348048780487812</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -35100,7 +35071,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>16.464859184531313</v>
+        <v>15.722451660361497</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35120,7 +35091,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>6.9509268292682922</v>
+        <v>6.6368349303135892</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35129,18 +35100,18 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>36.755707047443572</v>
+        <v>35.094824965453711</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="249" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="246"/>
-      <c r="E15" s="246" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="F15" s="246"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35191,14 +35162,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="246" t="s">
+      <c r="B21" s="249" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="E21" s="246" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>242</v>
       </c>
-      <c r="F21" s="246"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35267,14 +35238,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="246" t="s">
+      <c r="B29" s="249" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="246"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>249</v>
       </c>
-      <c r="F29" s="246"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35350,14 +35321,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="249" t="s">
         <v>261</v>
       </c>
-      <c r="C37" s="246"/>
-      <c r="E37" s="246" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="246"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35365,7 +35336,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.1722036563790053E-2</v>
+        <v>2.2747741952085638E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35381,7 +35352,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.6239658942042056E-2</v>
+        <v>3.7950880324884674E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35397,7 +35368,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.1057597798309418E-3</v>
+        <v>1.1579732894161242E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35422,18 +35393,18 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0754350134629458E-3</v>
+        <v>1.1262166003934032E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="246" t="s">
+      <c r="B45" s="249" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="246"/>
-      <c r="E45" s="246" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>278</v>
       </c>
-      <c r="F45" s="246"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35466,18 +35437,18 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>2.1383649686298107E-3</v>
+        <v>2.2393376589217666E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="246" t="s">
+      <c r="B51" s="249" t="s">
         <v>275</v>
       </c>
-      <c r="C51" s="246"/>
-      <c r="E51" s="246" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>296</v>
       </c>
-      <c r="F51" s="246"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35645,7 +35616,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>203.48</v>
+        <v>194.30500000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35674,7 +35645,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>79967.64</v>
+        <v>76361.865000000005</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35703,7 +35674,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>79796.639999999999</v>
+        <v>76190.865000000005</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35732,7 +35703,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>46.036199095022624</v>
+        <v>43.960407239819006</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35761,7 +35732,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>6.9480975609756097</v>
+        <v>6.6348048780487812</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35790,7 +35761,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>16.464859184531313</v>
+        <v>15.722451660361497</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35819,7 +35790,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>6.9509268292682922</v>
+        <v>6.6368349303135892</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35848,7 +35819,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>36.755707047443572</v>
+        <v>35.094824965453711</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36621,7 +36592,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.1722036563790053E-2</v>
+        <v>2.2747741952085638E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36650,7 +36621,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.6239658942042056E-2</v>
+        <v>3.7950880324884674E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36679,7 +36650,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.1057597798309418E-3</v>
+        <v>1.1579732894161242E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36737,7 +36708,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0754350134629458E-3</v>
+        <v>1.1262166003934032E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36973,7 +36944,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>2.1383649686298107E-3</v>
+        <v>2.2393376589217666E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37525,14 +37496,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="250" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37599,19 +37570,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="253">
         <f>Statement!AA88</f>
         <v>0.23547169811320753</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.24109173616376042</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37638,19 +37609,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="253">
         <f>Statement!AA89</f>
         <v>0.23575757575757575</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17049368541905854</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37677,19 +37648,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="253">
         <f>Statement!AA90</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.3783482142857143</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -37716,19 +37687,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="253">
         <f>Statement!AA93</f>
         <v>7.3214285714285718E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.32378854625550663</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -37755,19 +37726,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="253">
         <f>Statement!AA94</f>
         <v>0.44090909090909092</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43438914027149322</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -37794,19 +37765,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="253">
         <f>Statement!AA96</f>
         <v>0.27692307692307694</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.53703703703703709</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -37833,22 +37804,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.5510204081632651E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.6923076923076927E-3</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -37875,22 +37846,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.53012048192771088</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37939,22 +37910,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14167585446527012</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.29275905118601747</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37982,22 +37953,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.40077821011673154</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38025,22 +37996,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.50778816199376942</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.680672268907563E-2</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -38068,22 +38039,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="247">
+      <c r="C32" s="253">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.24629363940698232</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="F32" s="247">
+      <c r="D32" s="254"/>
+      <c r="F32" s="253">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.22982538933459179</v>
       </c>
-      <c r="G32" s="248"/>
+      <c r="G32" s="254"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -38111,43 +38082,25 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="247">
+      <c r="C34" s="253">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>0.1971326164874552</v>
       </c>
-      <c r="D34" s="248"/>
-      <c r="F34" s="247">
+      <c r="D34" s="254"/>
+      <c r="F34" s="253">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.28709055876685935</v>
       </c>
-      <c r="G34" s="248"/>
+      <c r="G34" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -38158,6 +38111,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE1E6A0-07FE-9B4F-945A-417095AD1570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D10C2D3-1D0A-5147-BE13-C6D9221D1C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="5" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="419">
   <si>
     <t>Ticker</t>
   </si>
@@ -1397,6 +1397,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -14741,11 +14753,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.1187999999999998</v>
-    <v>-1.2849999999999999</v>
-    <v>-6.5700000000000003E-3</v>
-    <v>0.19</v>
-    <v>9.7780000000000002E-4</v>
+    <v>2.1280999999999999</v>
+    <v>5.59</v>
+    <v>2.8767000000000001E-2</v>
+    <v>2.23</v>
+    <v>1.1162E-2</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14753,25 +14765,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>196.73</v>
+    <v>201.68</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46318.953736689065</v>
+    <v>46321.961294594534</v>
     <v>0</v>
-    <v>187.24</v>
-    <v>74805132201</v>
+    <v>194.55</v>
+    <v>76962991062</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>191.6</v>
-    <v>43.971400000000003</v>
-    <v>195.59</v>
-    <v>194.30500000000001</v>
-    <v>194.51</v>
+    <v>197.63499999999999</v>
+    <v>45.239800000000002</v>
+    <v>194.32</v>
+    <v>199.91</v>
+    <v>202.01</v>
     <v>384988200</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>7393446</v>
-    <v>5265947</v>
+    <v>5523470</v>
+    <v>5248398</v>
     <v>2016</v>
   </rv>
   <rv s="2">
@@ -14795,17 +14807,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15631,7 +15643,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>76361.865000000005</v>
+        <v>78564.63</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15658,7 +15670,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>76190.865000000005</v>
+        <v>78393.63</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15678,7 +15690,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15705,14 +15717,14 @@
       </c>
       <c r="C6" s="202" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>194.51</v>
+        <v>202.01</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>43.960407239819006</v>
+        <v>45.228506787330318</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15732,14 +15744,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.2849999999999999</v>
+        <v>5.59</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>6.6348048780487812</v>
+        <v>6.82619512195122</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15756,14 +15768,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.19</v>
+        <v>2.23</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.7950880324884674E-2</v>
+        <v>3.6886828080269704E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15780,14 +15792,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.5700000000000003E-3</v>
+        <v>2.8767000000000001E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>2.2747741952085638E-2</v>
+        <v>2.210994947726477E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15795,7 +15807,7 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.39881401994271326</v>
+        <v>0.35959460829857892</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -15804,7 +15816,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>9.7780000000000002E-4</v>
+        <v>1.1162E-2</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15827,7 +15839,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>1.1579732894161242E-3</v>
+        <v>1.1255064779150618E-3</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15859,7 +15871,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1187999999999998</v>
+        <v>2.1280999999999999</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15882,7 +15894,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5265947</v>
+        <v>5248398</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15905,7 +15917,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>2.2393376589217666E-3</v>
+        <v>2.1765519674693304E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16032,7 +16044,7 @@
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16047,7 +16059,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -21394,7 +21406,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21403,7 +21415,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>76361.865000000005</v>
+        <v>78564.63</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21421,7 +21433,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21430,7 +21442,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1187999999999998</v>
+        <v>2.1280999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21473,7 +21485,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>3.7073529103004071E-2</v>
+        <v>3.6071570412625639E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21482,7 +21494,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9629264708969959</v>
+        <v>0.96392842958737435</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21500,7 +21512,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.144876</v>
+        <v>0.14564449999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21509,7 +21521,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14117435641318146</v>
+        <v>0.14201517697871888</v>
       </c>
     </row>
   </sheetData>
@@ -23487,7 +23499,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23496,7 +23508,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.39881401994271326</v>
+        <v>0.35959460829857892</v>
       </c>
     </row>
   </sheetData>
@@ -24364,7 +24376,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24430,7 +24442,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>74807.425000000003</v>
+        <v>76965.350000000006</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24457,7 +24469,7 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>74636.425000000003</v>
+        <v>76794.350000000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -31091,7 +31103,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31162,7 +31174,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32272,7 +32284,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>43.960407239819006</v>
+        <v>45.228506787330318</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32309,7 +32321,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>6.6348048780487812</v>
+        <v>6.82619512195122</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32370,7 +32382,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>15.722451660361497</v>
+        <v>16.175987810004202</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32431,7 +32443,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>76361.865000000005</v>
+        <v>78564.63</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32492,7 +32504,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>76190.865000000005</v>
+        <v>78393.63</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32529,7 +32541,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>6.6368349303135892</v>
+        <v>6.828713414634147</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32566,7 +32578,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>35.094824965453711</v>
+        <v>36.10945647167204</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32701,7 +32713,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="135">AC147/AC151</f>
-        <v>26.349849896480332</v>
+        <v>27.109948240165632</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32738,7 +32750,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="135"/>
-        <v>26.50564703617097</v>
+        <v>27.271955590269041</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32775,7 +32787,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="138">AC151/AC147</f>
-        <v>3.7950880324884674E-2</v>
+        <v>3.6886828080269704E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32812,7 +32824,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.2747741952085638E-2</v>
+        <v>2.210994947726477E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32849,7 +32861,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>1.1579732894161242E-3</v>
+        <v>1.1255064779150618E-3</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -32923,7 +32935,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>1.1262166003934032E-3</v>
+        <v>1.0946401707740492E-3</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33426,7 +33438,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>2.2393376589217666E-3</v>
+        <v>2.1765519674693304E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -34942,7 +34954,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -34975,7 +34987,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34991,7 +35003,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>76361.865000000005</v>
+        <v>78564.63</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35011,7 +35023,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>76190.865000000005</v>
+        <v>78393.63</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -35031,7 +35043,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>43.960407239819006</v>
+        <v>45.228506787330318</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -35051,7 +35063,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>6.6348048780487812</v>
+        <v>6.82619512195122</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -35071,7 +35083,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>15.722451660361497</v>
+        <v>16.175987810004202</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35091,7 +35103,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>6.6368349303135892</v>
+        <v>6.828713414634147</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35100,7 +35112,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>35.094824965453711</v>
+        <v>36.10945647167204</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35336,7 +35348,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.2747741952085638E-2</v>
+        <v>2.210994947726477E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35352,7 +35364,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.7950880324884674E-2</v>
+        <v>3.6886828080269704E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35368,7 +35380,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.1579732894161242E-3</v>
+        <v>1.1255064779150618E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35393,7 +35405,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.1262166003934032E-3</v>
+        <v>1.0946401707740492E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35437,7 +35449,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>2.2393376589217666E-3</v>
+        <v>2.1765519674693304E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35491,8 +35503,51 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="249" t="s">
+        <v>415</v>
+      </c>
+      <c r="C57" s="249"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C58" s="168">
+        <f ca="1">Statement!AC153</f>
+        <v>27.109948240165632</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C59" s="168">
+        <f ca="1">Statement!AC154</f>
+        <v>27.271955590269041</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="C60" s="169">
+        <f>Statement!AC160</f>
+        <v>0.25039324341928432</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C61" s="169">
+        <f>Statement!AC161</f>
+        <v>0.2524390243902439</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -35517,7 +35572,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I97"/>
+  <dimension ref="B1:I106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -35616,7 +35671,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>194.30500000000001</v>
+        <v>199.91</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35645,7 +35700,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>76361.865000000005</v>
+        <v>78564.63</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35674,7 +35729,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>76190.865000000005</v>
+        <v>78393.63</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35703,7 +35758,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>43.960407239819006</v>
+        <v>45.228506787330318</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35732,7 +35787,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>6.6348048780487812</v>
+        <v>6.82619512195122</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35761,7 +35816,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>15.722451660361497</v>
+        <v>16.175987810004202</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35790,7 +35845,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>6.6368349303135892</v>
+        <v>6.828713414634147</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35819,7 +35874,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>35.094824965453711</v>
+        <v>36.10945647167204</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36592,7 +36647,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.2747741952085638E-2</v>
+        <v>2.210994947726477E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36621,7 +36676,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.7950880324884674E-2</v>
+        <v>3.6886828080269704E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36650,7 +36705,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.1579732894161242E-3</v>
+        <v>1.1255064779150618E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36708,7 +36763,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.1262166003934032E-3</v>
+        <v>1.0946401707740492E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36944,7 +36999,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>2.2393376589217666E-3</v>
+        <v>2.1765519674693304E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37281,197 +37336,361 @@
       </c>
       <c r="I85" s="191"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C88" s="168">
+        <f>Statement!M153</f>
+        <v>91.476634615384611</v>
+      </c>
+      <c r="D88" s="168">
+        <f>Statement!N153</f>
+        <v>-17.913979238754326</v>
+      </c>
+      <c r="E88" s="168">
+        <f>Statement!O153</f>
+        <v>25.149311740890688</v>
+      </c>
+      <c r="F88" s="168">
+        <f>Statement!P153</f>
+        <v>40.383190909090914</v>
+      </c>
+      <c r="G88" s="168">
+        <f>Statement!Q153</f>
+        <v>34.477698154180239</v>
+      </c>
+      <c r="I88" s="168">
+        <f ca="1">Statement!AC153</f>
+        <v>27.109948240165632</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C89" s="168">
+        <f>Statement!M154</f>
+        <v>60.728064496538316</v>
+      </c>
+      <c r="D89" s="168">
+        <f>Statement!N154</f>
+        <v>-52.243580165927057</v>
+      </c>
+      <c r="E89" s="168">
+        <f>Statement!O154</f>
+        <v>21.800913605547873</v>
+      </c>
+      <c r="F89" s="168">
+        <f>Statement!P154</f>
+        <v>42.215348624347172</v>
+      </c>
+      <c r="G89" s="168">
+        <f>Statement!Q154</f>
+        <v>35.445068643578196</v>
+      </c>
+      <c r="I89" s="168">
+        <f ca="1">Statement!AC154</f>
+        <v>27.271955590269041</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="190">
+        <f>Statement!M160</f>
+        <v>3.9692985627986135E-2</v>
+      </c>
+      <c r="D90" s="190">
+        <f>Statement!N160</f>
+        <v>-2.7262761897147381E-2</v>
+      </c>
+      <c r="E90" s="190">
+        <f>Statement!O160</f>
+        <v>0.13899669735665512</v>
+      </c>
+      <c r="F90" s="190">
+        <f>Statement!P160</f>
+        <v>0.13636163401955889</v>
+      </c>
+      <c r="G90" s="190">
+        <f>Statement!Q160</f>
+        <v>0.17813672445352755</v>
+      </c>
+      <c r="I90" s="190">
+        <f>Statement!AC160</f>
+        <v>0.25039324341928432</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C91" s="190">
+        <f>Statement!M161</f>
+        <v>2.0808323329331732E-2</v>
+      </c>
+      <c r="D91" s="190">
+        <f>Statement!N161</f>
+        <v>-5.0773014757554462E-2</v>
+      </c>
+      <c r="E91" s="190">
+        <f>Statement!O161</f>
+        <v>0.10797027538977123</v>
+      </c>
+      <c r="F91" s="190">
+        <f>Statement!P161</f>
+        <v>0.13729405891163254</v>
+      </c>
+      <c r="G91" s="190">
+        <f>Statement!Q161</f>
+        <v>0.18005865102639296</v>
+      </c>
+      <c r="I91" s="190">
+        <f>Statement!AC161</f>
+        <v>0.2524390243902439</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C94" s="169">
+        <f>Statement!M202</f>
+        <v>-1</v>
+      </c>
+      <c r="D94" s="169">
+        <f>Statement!N202</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="169">
+        <f>Statement!O202</f>
+        <v>1.5</v>
+      </c>
+      <c r="F94" s="169">
+        <f>Statement!P202</f>
+        <v>3.2</v>
+      </c>
+      <c r="G94" s="169">
+        <f>Statement!Q202</f>
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="I94" s="191"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B193</f>
         <v>Americas</v>
       </c>
-      <c r="C89" s="169">
+      <c r="C98" s="169">
         <f>Statement!M193</f>
         <v>1</v>
       </c>
-      <c r="D89" s="169">
+      <c r="D98" s="169">
         <f>Statement!N193</f>
         <v>0.24782807498856882</v>
       </c>
-      <c r="E89" s="169">
+      <c r="E98" s="169">
         <f>Statement!O193</f>
         <v>0.40894100403078049</v>
       </c>
-      <c r="F89" s="169">
+      <c r="F98" s="169">
         <f>Statement!P193</f>
         <v>0.1706111833550065</v>
       </c>
-      <c r="G89" s="169">
+      <c r="G98" s="169">
         <f>Statement!Q193</f>
         <v>0.41879582315041103</v>
       </c>
-      <c r="I89" s="191"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="191"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B194</f>
         <v>Asia Pacific</v>
       </c>
-      <c r="C90" s="169">
+      <c r="C99" s="169">
         <f>Statement!M194</f>
         <v>1</v>
       </c>
-      <c r="D90" s="169">
+      <c r="D99" s="169">
         <f>Statement!N194</f>
         <v>-4.972032318210068E-3</v>
       </c>
-      <c r="E90" s="169">
+      <c r="E99" s="169">
         <f>Statement!O194</f>
         <v>-4.5596502186133668E-2</v>
       </c>
-      <c r="F90" s="169">
+      <c r="F99" s="169">
         <f>Statement!P194</f>
         <v>0.1243455497382199</v>
       </c>
-      <c r="G90" s="169">
+      <c r="G99" s="169">
         <f>Statement!Q194</f>
         <v>0.17520372526193248</v>
       </c>
-      <c r="I90" s="191"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
+      <c r="I99" s="191"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
         <f>Statement!B195</f>
         <v>Europe Middle East Africa</v>
       </c>
-      <c r="C91" s="169">
+      <c r="C100" s="169">
         <f>Statement!M195</f>
         <v>1</v>
       </c>
-      <c r="D91" s="169">
+      <c r="D100" s="169">
         <f>Statement!N195</f>
         <v>0.13311148086522462</v>
       </c>
-      <c r="E91" s="169">
+      <c r="E100" s="169">
         <f>Statement!O195</f>
         <v>9.4713656387665199E-2</v>
       </c>
-      <c r="F91" s="169">
+      <c r="F100" s="169">
         <f>Statement!P195</f>
         <v>0.20254862508383636</v>
       </c>
-      <c r="G91" s="169">
+      <c r="G100" s="169">
         <f>Statement!Q195</f>
         <v>1.7289459007250419E-2</v>
       </c>
-      <c r="I91" s="191"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20"/>
-      <c r="C92" s="169"/>
-      <c r="D92" s="169"/>
-      <c r="E92" s="169"/>
-      <c r="F92" s="169"/>
-      <c r="G92" s="169"/>
-      <c r="I92" s="191"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="str">
+      <c r="I100" s="191"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20"/>
+      <c r="C101" s="169"/>
+      <c r="D101" s="169"/>
+      <c r="E101" s="169"/>
+      <c r="F101" s="169"/>
+      <c r="G101" s="169"/>
+      <c r="I101" s="191"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="str">
         <f>Statement!B197</f>
         <v>Products</v>
       </c>
-      <c r="C93" s="169">
+      <c r="C102" s="169">
         <f>Statement!M197</f>
         <v>1</v>
       </c>
-      <c r="D93" s="169">
+      <c r="D102" s="169">
         <f>Statement!N197</f>
         <v>0.18319752739533576</v>
       </c>
-      <c r="E93" s="169">
+      <c r="E102" s="169">
         <f>Statement!O197</f>
         <v>0.25172168131085254</v>
       </c>
-      <c r="F93" s="169">
+      <c r="F102" s="169">
         <f>Statement!P197</f>
         <v>0.18478467084044772</v>
       </c>
-      <c r="G93" s="169">
+      <c r="G102" s="169">
         <f>Statement!Q197</f>
         <v>0.31417133706965572</v>
       </c>
-      <c r="I93" s="191"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B94" s="20" t="str">
+      <c r="I102" s="191"/>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B103" s="20" t="str">
         <f>Statement!B198</f>
         <v>Services</v>
       </c>
-      <c r="C94" s="169">
+      <c r="C103" s="169">
         <f>Statement!M198</f>
         <v>1</v>
       </c>
-      <c r="D94" s="169">
+      <c r="D103" s="169">
         <f>Statement!N198</f>
         <v>2.9186935371785964E-2</v>
       </c>
-      <c r="E94" s="169">
+      <c r="E103" s="169">
         <f>Statement!O198</f>
         <v>7.4949358541525998E-2</v>
       </c>
-      <c r="F94" s="169">
+      <c r="F103" s="169">
         <f>Statement!P198</f>
         <v>0.10992462311557789</v>
       </c>
-      <c r="G94" s="169">
+      <c r="G103" s="169">
         <f>Statement!Q198</f>
         <v>0.14487832484436899</v>
       </c>
-      <c r="I94" s="191"/>
-    </row>
-    <row r="96" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
-      <c r="I96" s="14"/>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B97" s="20" t="s">
+      <c r="I103" s="191"/>
+    </row>
+    <row r="105" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="I105" s="14"/>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B106" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C97" s="169">
+      <c r="C106" s="169">
         <f>Statement!M202</f>
         <v>-1</v>
       </c>
-      <c r="D97" s="169">
+      <c r="D106" s="169">
         <f>Statement!N202</f>
         <v>0</v>
       </c>
-      <c r="E97" s="169">
+      <c r="E106" s="169">
         <f>Statement!O202</f>
         <v>1.5</v>
       </c>
-      <c r="F97" s="169">
+      <c r="F106" s="169">
         <f>Statement!P202</f>
         <v>3.2</v>
       </c>
-      <c r="G97" s="169">
+      <c r="G106" s="169">
         <f>Statement!Q202</f>
         <v>0.59523809523809523</v>
       </c>
-      <c r="I97" s="191"/>
+      <c r="I106" s="191"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VRT.xlsx
+++ b/VRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB745B58-889D-B942-B369-7A5880CA0107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C7FA60-3F56-C34D-81B5-213ED63BDFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1647,7 +1617,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1753,12 +1723,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2072,7 +2036,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2413,6 +2377,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2420,12 +2390,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2446,18 +2410,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="37" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -14782,7 +14743,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=b19hc7&amp;q=XNYS%3aVRT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -14801,9 +14762,11 @@
     <v>Powered by Refinitiv</v>
     <v>379.935</v>
     <v>147.82</v>
-    <v>2.1038999999999999</v>
-    <v>32.42</v>
-    <v>0.155447</v>
+    <v>2.1114999999999999</v>
+    <v>-13.42</v>
+    <v>-5.4570999999999995E-2</v>
+    <v>1.4469000000000001</v>
+    <v>6.2229999999999994E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -14811,49 +14774,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>505 N. Cleveland Ave., WESTERVILLE, OH, 43082 US</v>
-    <v>241.55</v>
+    <v>240.78469999999999</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46323.768517383593</v>
+    <v>46325.999697233594</v>
     <v>0</v>
-    <v>228.82</v>
-    <v>92774456436</v>
+    <v>226.86</v>
+    <v>89526543000</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
-    <v>240.26</v>
-    <v>54.533900000000003</v>
-    <v>208.56</v>
-    <v>240.98</v>
-    <v>384988200</v>
+    <v>231.22</v>
+    <v>45.997399999999999</v>
+    <v>245.92</v>
+    <v>232.5</v>
+    <v>233.9469</v>
+    <v>385060400</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>13546354</v>
-    <v>5471268</v>
+    <v>7667493</v>
+    <v>6332297</v>
     <v>2016</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -14866,29 +14815,29 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
-    <v>39.47</v>
-    <v>7.0000000000000007E-2</v>
-    <v>1.4039999999999999E-3</v>
+    <v>39.56</v>
+    <v>-0.6</v>
+    <v>-1.2025999999999998E-2</v>
     <v>US</v>
-    <v>50.07</v>
+    <v>49.58</v>
     <v>Index</v>
-    <v>6</v>
-    <v>49.72</v>
+    <v>3</v>
+    <v>49.08</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.76</v>
-    <v>49.86</v>
-    <v>49.93</v>
+    <v>49.21</v>
+    <v>49.89</v>
+    <v>49.29</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -14910,6 +14859,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -14930,6 +14881,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -14939,11 +14891,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -14979,7 +14926,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -14990,13 +14937,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15090,13 +15040,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15168,6 +15124,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15175,6 +15134,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -15690,7 +15652,7 @@
       </c>
       <c r="F3" s="181">
         <f ca="1">Statement!AC147</f>
-        <v>94705.14</v>
+        <v>91372.5</v>
       </c>
       <c r="H3" s="179" t="str">
         <f>'AVG target price'!B5</f>
@@ -15717,7 +15679,7 @@
       </c>
       <c r="F4" s="182">
         <f ca="1">Statement!AC148</f>
-        <v>93921.14</v>
+        <v>90588.5</v>
       </c>
       <c r="H4" s="179" t="str">
         <f>'AVG target price'!B6</f>
@@ -15737,7 +15699,7 @@
       </c>
       <c r="C5" s="202" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
       <c r="E5" s="179" t="s">
         <v>236</v>
@@ -15762,16 +15724,16 @@
       <c r="B6" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="202" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="202" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>233.9469</v>
       </c>
       <c r="E6" s="179" t="s">
         <v>230</v>
       </c>
       <c r="F6" s="184">
         <f ca="1">Statement!AC144</f>
-        <v>45.04299065420561</v>
+        <v>43.45794392523365</v>
       </c>
       <c r="H6" s="179" t="str">
         <f>'AVG target price'!B8</f>
@@ -15791,14 +15753,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>32.42</v>
+        <v>-13.42</v>
       </c>
       <c r="E7" s="180" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="185">
         <f ca="1">Statement!AC145</f>
-        <v>7.2113944800243974</v>
+        <v>6.9576280878316563</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -15813,16 +15775,16 @@
       <c r="B8" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>1.4469000000000001</v>
       </c>
       <c r="E8" s="179" t="s">
         <v>258</v>
       </c>
       <c r="F8" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>3.2543112232345572E-2</v>
+        <v>3.3730061013981232E-2</v>
       </c>
       <c r="H8" s="178" t="str">
         <f>'AVG target price'!B10</f>
@@ -15839,14 +15801,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>0.155447</v>
+        <v>-5.4570999999999995E-2</v>
       </c>
       <c r="E9" s="179" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="186">
         <f ca="1">Statement!AC156</f>
-        <v>2.2201012532160346E-2</v>
+        <v>2.3010752688172043E-2</v>
       </c>
       <c r="H9" s="178" t="str">
         <f>'AVG target price'!B12</f>
@@ -15854,16 +15816,16 @@
       </c>
       <c r="I9" s="207">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.22066814526300135</v>
+        <v>0.26518971890528198</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>6.2229999999999994E-3</v>
       </c>
       <c r="E10" s="179" t="s">
         <v>286</v>
@@ -15886,7 +15848,7 @@
       </c>
       <c r="F11" s="187">
         <f ca="1">Statement!AC157</f>
-        <v>1.0374304921570256E-3</v>
+        <v>1.0752688172043011E-3</v>
       </c>
       <c r="H11" s="178" t="s">
         <v>359</v>
@@ -15918,7 +15880,7 @@
       </c>
       <c r="C13" s="203" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1038999999999999</v>
+        <v>2.1114999999999999</v>
       </c>
       <c r="E13" s="179" t="s">
         <v>100</v>
@@ -15941,7 +15903,7 @@
       </c>
       <c r="C14" s="204" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5471268</v>
+        <v>6332297</v>
       </c>
       <c r="E14" s="180" t="s">
         <v>101</v>
@@ -15964,7 +15926,7 @@
       </c>
       <c r="F15" s="186">
         <f ca="1">Statement!AC170</f>
-        <v>8.2783257592988092E-3</v>
+        <v>8.5802621138745244E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16086,12 +16048,12 @@
       <c r="C26" s="164">
         <v>0.21</v>
       </c>
-      <c r="E26" s="179" t="e" vm="5">
+      <c r="E26" s="179" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="213" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.93</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16106,7 +16068,7 @@
       </c>
       <c r="F27" s="214">
         <f ca="1">F26/1000</f>
-        <v>4.9930000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20278,6 +20240,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20285,12 +20253,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21350,16 +21312,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21481,7 +21443,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21490,7 +21452,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>94705.14</v>
+        <v>91372.5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21508,7 +21470,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9930000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21517,7 +21479,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1038999999999999</v>
+        <v>2.1114999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21560,7 +21522,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.9989816982225501E-2</v>
+        <v>3.1049676300761928E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21569,7 +21531,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97001018301777453</v>
+        <v>0.96895032369923806</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21587,7 +21549,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1446055</v>
+        <v>0.14430749999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21596,7 +21558,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14169032484533428</v>
+        <v>0.14129855349388387</v>
       </c>
     </row>
   </sheetData>
@@ -23460,17 +23422,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23574,7 +23536,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23583,7 +23545,7 @@
       </c>
       <c r="C12" s="149">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.22066814526300135</v>
+        <v>0.26518971890528198</v>
       </c>
     </row>
   </sheetData>
@@ -24440,10 +24402,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="262" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="262"/>
+      <c r="C14" s="263"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="150" t="s">
@@ -24451,7 +24413,7 @@
       </c>
       <c r="C15" s="151">
         <f ca="1">Overview!C5</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24470,20 +24432,20 @@
       <c r="C17" s="153">
         <v>0.44</v>
       </c>
-      <c r="E17" s="263" t="s">
+      <c r="E17" s="261" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="263"/>
-      <c r="I17" s="263"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="261" t="s">
+      <c r="B19" s="262" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="262"/>
+      <c r="C19" s="263"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="154" t="s">
@@ -24517,7 +24479,7 @@
       </c>
       <c r="C23" s="156">
         <f ca="1">C15*C22</f>
-        <v>92777.3</v>
+        <v>89512.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24544,15 +24506,15 @@
       </c>
       <c r="C26" s="157">
         <f ca="1">C23+C25-C24</f>
-        <v>91993.3</v>
+        <v>88728.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="261" t="s">
+      <c r="B28" s="262" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="262"/>
+      <c r="C28" s="263"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="154" t="s">
@@ -24628,16 +24590,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25009,7 +24971,7 @@
         <v>1235</v>
       </c>
       <c r="AA7" s="22">
-        <f t="shared" ref="Z7:AA7" si="3">AA5-AA6</f>
+        <f t="shared" ref="AA7" si="3">AA5-AA6</f>
         <v>1643</v>
       </c>
       <c r="AB7" s="16"/>
@@ -25199,7 +25161,7 @@
         <v>601</v>
       </c>
       <c r="AA10" s="25">
-        <f t="shared" ref="T10:AA10" si="8">AA7-AA11</f>
+        <f t="shared" ref="AA10" si="8">AA7-AA11</f>
         <v>659</v>
       </c>
       <c r="AC10" s="21">
@@ -25756,7 +25718,7 @@
         <v>382</v>
       </c>
       <c r="T19" s="25">
-        <f t="shared" ref="T19:Z19" si="10">T18*T$84</f>
+        <f t="shared" ref="T19:Y19" si="10">T18*T$84</f>
         <v>377</v>
       </c>
       <c r="U19" s="25">
@@ -25915,7 +25877,7 @@
         <v>391</v>
       </c>
       <c r="T21" s="25">
-        <f t="shared" ref="T21:Z21" si="13">T20*T$84</f>
+        <f t="shared" ref="T21:Y21" si="13">T20*T$84</f>
         <v>386</v>
       </c>
       <c r="U21" s="25">
@@ -26044,7 +26006,7 @@
         <v>3.49</v>
       </c>
       <c r="T23" s="65">
-        <f t="shared" ref="T23:Z23" si="15">T22/T$84</f>
+        <f t="shared" ref="T23:Y23" si="15">T22/T$84</f>
         <v>0.39</v>
       </c>
       <c r="U23" s="65">
@@ -26176,7 +26138,7 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="66">
-        <f t="shared" ref="T25:Z25" si="17">T24/T$84</f>
+        <f t="shared" ref="T25:Y25" si="17">T24/T$84</f>
         <v>0.38</v>
       </c>
       <c r="U25" s="66">
@@ -26723,7 +26685,7 @@
         <v>5916</v>
       </c>
       <c r="AA35" s="222">
-        <f t="shared" ref="Z35:AA35" si="22">AA36-AA31</f>
+        <f t="shared" ref="AA35" si="22">AA36-AA31</f>
         <v>6052</v>
       </c>
       <c r="AB35" s="1"/>
@@ -27102,7 +27064,7 @@
         <v>3900</v>
       </c>
       <c r="AA41" s="222">
-        <f t="shared" ref="Z41:AA41" si="25">AA42-AA39</f>
+        <f t="shared" ref="AA41" si="25">AA42-AA39</f>
         <v>3962</v>
       </c>
       <c r="AB41" s="1"/>
@@ -27786,12 +27748,12 @@
       <c r="Z54" s="62">
         <v>-587</v>
       </c>
-      <c r="AA54" s="264">
-        <v>-587</v>
+      <c r="AA54" s="62">
+        <v>-631</v>
       </c>
       <c r="AC54" s="62">
         <f t="shared" si="26"/>
-        <v>-1440</v>
+        <v>-1484</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
@@ -27844,12 +27806,12 @@
       <c r="Z55" s="62">
         <v>-664</v>
       </c>
-      <c r="AA55" s="264">
-        <v>-664</v>
+      <c r="AA55" s="62">
+        <v>-767</v>
       </c>
       <c r="AC55" s="62">
         <f>SUM(X55:AA55)</f>
-        <v>-1734</v>
+        <v>-1837</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
@@ -27902,12 +27864,12 @@
       <c r="Z56" s="62">
         <v>483</v>
       </c>
-      <c r="AA56" s="264">
-        <v>483</v>
+      <c r="AA56" s="62">
+        <v>723</v>
       </c>
       <c r="AC56" s="62">
         <f t="shared" si="26"/>
-        <v>1188</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
@@ -27972,13 +27934,12 @@
         <f>-57+1172+118-14</f>
         <v>1219</v>
       </c>
-      <c r="AA57" s="264">
-        <f>-57+1172+118-14</f>
-        <v>1219</v>
+      <c r="AA57" s="62">
+        <v>536</v>
       </c>
       <c r="AC57" s="62">
         <f t="shared" si="26"/>
-        <v>3621</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.2">
@@ -28570,7 +28531,7 @@
         <v>494</v>
       </c>
       <c r="AA68" s="64">
-        <f t="shared" ref="T68:AA68" si="30">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
+        <f t="shared" ref="AA68" si="30">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
         <v>765</v>
       </c>
       <c r="AC68" s="64">
@@ -28674,7 +28635,7 @@
         <v>4</v>
       </c>
       <c r="AA69" s="40">
-        <f t="shared" ref="Z69:AA69" si="33">AA17-AA68</f>
+        <f t="shared" ref="AA69" si="33">AA17-AA68</f>
         <v>0</v>
       </c>
       <c r="AB69" s="16"/>
@@ -28753,7 +28714,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="42">
-        <f t="shared" ref="T70:Z70" si="35">T36-(T42+T110)</f>
+        <f t="shared" ref="T70:Y70" si="35">T36-(T42+T110)</f>
         <v>1</v>
       </c>
       <c r="U70" s="42">
@@ -28863,7 +28824,7 @@
       <c r="Z73" s="21">
         <v>385</v>
       </c>
-      <c r="AA73" s="265">
+      <c r="AA73" s="21">
         <v>385</v>
       </c>
       <c r="AC73" s="24">
@@ -28906,11 +28867,11 @@
         <v>383</v>
       </c>
       <c r="T74" s="25">
-        <f t="shared" ref="T74:U74" si="38">T73*T84</f>
+        <f t="shared" ref="T74" si="38">T73*T84</f>
         <v>381</v>
       </c>
       <c r="U74" s="25">
-        <f t="shared" ref="U74:V74" si="39">U73*U84</f>
+        <f t="shared" ref="U74" si="39">U73*U84</f>
         <v>381</v>
       </c>
       <c r="V74" s="25">
@@ -28992,7 +28953,7 @@
       <c r="Z75" s="21">
         <v>8</v>
       </c>
-      <c r="AA75" s="265">
+      <c r="AA75" s="21">
         <v>8</v>
       </c>
       <c r="AC75" s="21">
@@ -29063,7 +29024,7 @@
         <v>8</v>
       </c>
       <c r="AA76" s="25">
-        <f t="shared" ref="Z76:AA76" si="44">AA75*AA84</f>
+        <f t="shared" ref="AA76" si="44">AA75*AA84</f>
         <v>8</v>
       </c>
       <c r="AC76" s="24">
@@ -29134,7 +29095,7 @@
         <v>393</v>
       </c>
       <c r="AA77" s="25">
-        <f t="shared" ref="Z77:AA77" si="47">AA74+AA76</f>
+        <f t="shared" ref="AA77" si="47">AA74+AA76</f>
         <v>393</v>
       </c>
       <c r="AC77" s="24">
@@ -29281,7 +29242,7 @@
       <c r="Z80" s="223">
         <v>6.25E-2</v>
       </c>
-      <c r="AA80" s="266">
+      <c r="AA80" s="223">
         <v>6.25E-2</v>
       </c>
       <c r="AC80" s="72">
@@ -29324,11 +29285,11 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="T81" s="45">
-        <f t="shared" ref="T81:U81" si="50">T80/T84</f>
+        <f t="shared" ref="T81" si="50">T80/T84</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="U81" s="45">
-        <f t="shared" ref="U81:V81" si="51">U80/U84</f>
+        <f t="shared" ref="U81" si="51">U80/U84</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="V81" s="45">
@@ -29425,7 +29386,7 @@
         <v>0.23478760045924224</v>
       </c>
       <c r="T82" s="46">
-        <f t="shared" ref="T82:Z82" si="55">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
+        <f t="shared" ref="T82:Y82" si="55">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
         <v>0.4</v>
       </c>
       <c r="U82" s="46">
@@ -29664,7 +29625,7 @@
         <v>0.23547169811320753</v>
       </c>
       <c r="AA88" s="48">
-        <f t="shared" ref="T88:AA92" si="65">IF(Z5=0,
+        <f t="shared" ref="AA88:AA92" si="65">IF(Z5=0,
 IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
 (AA5-Z5)/ABS(Z5)
 )</f>
@@ -30406,7 +30367,7 @@
         <v>0.37721441661576055</v>
       </c>
       <c r="AA99" s="50">
-        <f t="shared" ref="T99:AA99" si="85">AA7/AA5</f>
+        <f t="shared" ref="AA99" si="85">AA7/AA5</f>
         <v>0.38102968460111319</v>
       </c>
       <c r="AC99" s="50">
@@ -30477,7 +30438,7 @@
         <v>0.19364691508857668</v>
       </c>
       <c r="AA100" s="50">
-        <f t="shared" ref="T100:AA100" si="87">AA11/AA5</f>
+        <f t="shared" ref="AA100" si="87">AA11/AA5</f>
         <v>0.22820037105751392</v>
       </c>
       <c r="AC100" s="50">
@@ -30551,7 +30512,7 @@
         <v>0.15210751374465487</v>
       </c>
       <c r="AA101" s="55">
-        <f t="shared" ref="T101:AA101" si="89">AA109/AA5</f>
+        <f t="shared" ref="AA101" si="89">AA109/AA5</f>
         <v>0.17741187384044527</v>
       </c>
       <c r="AB101" s="1"/>
@@ -30641,7 +30602,7 @@
         <v>0.23478760045924224</v>
       </c>
       <c r="T104" s="81">
-        <f t="shared" ref="T104:Z104" si="91">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
+        <f t="shared" ref="T104:Y104" si="91">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
         <v>0.4</v>
       </c>
       <c r="U104" s="81">
@@ -30712,7 +30673,7 @@
         <v>1828</v>
       </c>
       <c r="T105" s="25">
-        <f t="shared" ref="T105:Z105" si="93">T28+T33</f>
+        <f t="shared" ref="T105:Y105" si="93">T28+T33</f>
         <v>1228</v>
       </c>
       <c r="U105" s="25">
@@ -30803,7 +30764,7 @@
         <v>2913</v>
       </c>
       <c r="T106" s="25">
-        <f t="shared" ref="T106:Z106" si="95">T38+T40</f>
+        <f t="shared" ref="T106:Y106" si="95">T38+T40</f>
         <v>2928</v>
       </c>
       <c r="U106" s="25">
@@ -30921,7 +30882,7 @@
         <v>-226</v>
       </c>
       <c r="T108" s="126">
-        <f t="shared" ref="T108:Z108" si="97">T59+T60</f>
+        <f t="shared" ref="T108:Y108" si="97">T59+T60</f>
         <v>-64</v>
       </c>
       <c r="U108" s="126">
@@ -30992,7 +30953,7 @@
         <v>1333</v>
       </c>
       <c r="T109" s="126">
-        <f t="shared" ref="T109:Z109" si="99">T16+T17</f>
+        <f t="shared" ref="T109:Y109" si="99">T16+T17</f>
         <v>147</v>
       </c>
       <c r="U109" s="126">
@@ -31063,7 +31024,7 @@
         <v>3941</v>
       </c>
       <c r="T110" s="126">
-        <f t="shared" ref="T110:Z110" si="101">T48+T47</f>
+        <f t="shared" ref="T110:Y110" si="101">T48+T47</f>
         <v>2434</v>
       </c>
       <c r="U110" s="126">
@@ -31179,7 +31140,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31217,7 +31178,7 @@
         <v>162.01</v>
       </c>
       <c r="T115" s="65">
-        <f t="shared" ref="T115:Z115" si="103">T114/T84</f>
+        <f t="shared" ref="T115:Y115" si="103">T114/T84</f>
         <v>113.61</v>
       </c>
       <c r="U115" s="65">
@@ -31250,7 +31211,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31640,7 +31601,7 @@
         <v>4312</v>
       </c>
       <c r="AA129" s="25">
-        <f t="shared" ref="T129:AA129" si="114">AB5</f>
+        <f t="shared" ref="AA129" si="114">AB5</f>
         <v>0</v>
       </c>
       <c r="AC129" s="49"/>
@@ -31665,7 +31626,7 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="233" t="str">
-        <f t="shared" ref="T130:Y130" si="115">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
+        <f t="shared" ref="T130:X130" si="115">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U130" s="233" t="str">
@@ -31830,7 +31791,7 @@
         <v>103.08491142333537</v>
       </c>
       <c r="AA135" s="118">
-        <f t="shared" ref="T135:AA135" si="118">AA29/AA5*90</f>
+        <f t="shared" ref="AA135" si="118">AA29/AA5*90</f>
         <v>91.419294990723571</v>
       </c>
       <c r="AC135" s="118">
@@ -31891,7 +31852,7 @@
         <v>451.64051005394805</v>
       </c>
       <c r="AA136" s="118">
-        <f t="shared" ref="T136:AA136" si="120">AA30/AA6*365</f>
+        <f t="shared" ref="AA136" si="120">AA30/AA6*365</f>
         <v>449.65155488947175</v>
       </c>
       <c r="AC136" s="118">
@@ -31952,7 +31913,7 @@
         <v>109.15644923982343</v>
       </c>
       <c r="AA137" s="118">
-        <f t="shared" ref="T137:AA137" si="122">AA37/AA6*90</f>
+        <f t="shared" ref="AA137" si="122">AA37/AA6*90</f>
         <v>109.4230048707381</v>
       </c>
       <c r="AC137" s="118">
@@ -31985,11 +31946,11 @@
         <v>94.175831921072415</v>
       </c>
       <c r="T138" s="118">
-        <f t="shared" ref="T138:U138" si="124">T135+T136-T137</f>
+        <f t="shared" ref="T138" si="124">T135+T136-T137</f>
         <v>318.03699776128201</v>
       </c>
       <c r="U138" s="118">
-        <f t="shared" ref="U138:V138" si="125">U135+U136-U137</f>
+        <f t="shared" ref="U138" si="125">U135+U136-U137</f>
         <v>382.54878119770063</v>
       </c>
       <c r="V138" s="118">
@@ -32046,7 +32007,7 @@
         <v>0.7391524993656432</v>
       </c>
       <c r="T139" s="118">
-        <f t="shared" ref="T139:Z139" si="129">T106/T48</f>
+        <f t="shared" ref="T139:Y139" si="129">T106/T48</f>
         <v>1.2029580936729662</v>
       </c>
       <c r="U139" s="118">
@@ -32107,7 +32068,7 @@
         <v>0.27531083481349911</v>
       </c>
       <c r="T140" s="173">
-        <f t="shared" ref="T140:Z140" si="131">(T106-T105)/T48</f>
+        <f t="shared" ref="T140:Y140" si="131">(T106-T105)/T48</f>
         <v>0.69843878389482339</v>
       </c>
       <c r="U140" s="173">
@@ -32168,7 +32129,7 @@
         <v>1.1202632176083505</v>
       </c>
       <c r="T141" s="118">
-        <f t="shared" ref="T141:Z141" si="133">(T105+T29)/T39</f>
+        <f t="shared" ref="T141:Y141" si="133">(T105+T29)/T39</f>
         <v>1.1595092024539877</v>
       </c>
       <c r="U141" s="118">
@@ -32229,7 +32190,7 @@
         <v>1.5475380077149989</v>
       </c>
       <c r="T142" s="118">
-        <f t="shared" ref="T142:Z142" si="135">T31/T39</f>
+        <f t="shared" ref="T142:Y142" si="135">T31/T39</f>
         <v>1.6474007103648691</v>
       </c>
       <c r="U142" s="118">
@@ -32290,7 +32251,7 @@
         <v>21.279069767441861</v>
       </c>
       <c r="T143" s="175">
-        <f t="shared" ref="T143:Z143" si="137">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T143:Y143" si="137">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>14.741935483870968</v>
       </c>
       <c r="U143" s="175">
@@ -32360,7 +32321,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>45.04299065420561</v>
+        <v>43.45794392523365</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32397,7 +32358,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>7.2113944800243974</v>
+        <v>6.9576280878316563</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32458,7 +32419,7 @@
       </c>
       <c r="AC146" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>16.862468193384224</v>
+        <v>16.269083969465647</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32519,7 +32480,7 @@
       </c>
       <c r="AC147" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>94705.14</v>
+        <v>91372.5</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -32547,7 +32508,7 @@
         <v>64592.92</v>
       </c>
       <c r="T148" s="141">
-        <f t="shared" ref="T148:Z148" si="139">T147+T106-T105+T47+T44</f>
+        <f t="shared" ref="T148:Y148" si="139">T147+T106-T105+T47+T44</f>
         <v>46121.51</v>
       </c>
       <c r="U148" s="141">
@@ -32580,7 +32541,7 @@
       </c>
       <c r="AC148" s="141">
         <f ca="1">AC147+AC106-AC105+AC47+AC44</f>
-        <v>93921.14</v>
+        <v>90588.5</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -32617,7 +32578,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="177">
         <f ca="1">AC148/AC5</f>
-        <v>7.1608066483684052</v>
+        <v>6.9067169868862459</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32654,7 +32615,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="177">
         <f ca="1">AC148/AC11</f>
-        <v>35.603161485974219</v>
+        <v>34.339840788476117</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32682,7 +32643,7 @@
         <v>1842</v>
       </c>
       <c r="T151" s="64">
-        <f t="shared" ref="T151:Z151" si="141">T58-T53+T108+T64</f>
+        <f t="shared" ref="T151:Y151" si="141">T58-T53+T108+T64</f>
         <v>352</v>
       </c>
       <c r="U151" s="64">
@@ -32752,7 +32713,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="64">
         <f>AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
-        <v>3644.6437308868499</v>
+        <v>3054.6437308868499</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32789,7 +32750,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f t="shared" ref="AC153:AC154" ca="1" si="144">AC147/AC151</f>
-        <v>30.728468526930563</v>
+        <v>29.647144711226478</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32826,7 +32787,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f t="shared" ca="1" si="144"/>
-        <v>25.769635370408675</v>
+        <v>29.655995258635148</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32863,7 +32824,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="74">
         <f t="shared" ref="AC155" ca="1" si="147">AC151/AC147</f>
-        <v>3.2543112232345572E-2</v>
+        <v>3.3730061013981232E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32900,7 +32861,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.2201012532160346E-2</v>
+        <v>2.3010752688172043E-2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32937,7 +32898,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="149">
         <f ca="1">AC81/AC115</f>
-        <v>1.0374304921570256E-3</v>
+        <v>1.0752688172043011E-3</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -33011,7 +32972,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="149">
         <f ca="1">-(AC62+AC63)/AC147</f>
-        <v>1.0136725419549561E-3</v>
+        <v>1.0506443404744315E-3</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33048,7 +33009,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="149">
         <f>AC152/AC5</f>
-        <v>0.27787768609994279</v>
+        <v>0.2328944595064692</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33261,7 +33222,7 @@
         <v>4.7728459530026113</v>
       </c>
       <c r="T166" s="72">
-        <f t="shared" ref="T166:Z166" si="148">T105/T74</f>
+        <f t="shared" ref="T166:Y166" si="148">T105/T74</f>
         <v>3.2230971128608923</v>
       </c>
       <c r="U166" s="72">
@@ -33322,7 +33283,7 @@
         <v>2.1759697256385997E-2</v>
       </c>
       <c r="T167" s="149">
-        <f t="shared" ref="T167:Z167" si="150">T53/T58</f>
+        <f t="shared" ref="T167:Y167" si="150">T53/T58</f>
         <v>2.1176470588235293E-2</v>
       </c>
       <c r="U167" s="149">
@@ -33411,7 +33372,7 @@
         <v>4.2761148442272447E-3</v>
       </c>
       <c r="AA168" s="149">
-        <f t="shared" ref="T168:AA168" si="153">AA53/AA5</f>
+        <f t="shared" ref="AA168" si="153">AA53/AA5</f>
         <v>4.6382189239332098E-3</v>
       </c>
       <c r="AC168" s="149">
@@ -33444,7 +33405,7 @@
         <v>-2.8328981723237598</v>
       </c>
       <c r="T169" s="72">
-        <f t="shared" ref="T169:Z169" si="154">(T105-T106)/T74</f>
+        <f t="shared" ref="T169:Y169" si="154">(T105-T106)/T74</f>
         <v>-4.4619422572178475</v>
       </c>
       <c r="U169" s="72">
@@ -33514,7 +33475,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="149">
         <f ca="1">(AC105-AC106)/AC147</f>
-        <v>8.2783257592988092E-3</v>
+        <v>8.5802621138745244E-3</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -33570,7 +33531,7 @@
         <v>5.3145998778252899E-2</v>
       </c>
       <c r="AA171" s="149">
-        <f t="shared" ref="T171:AA171" si="157">-AA108/AA5</f>
+        <f t="shared" ref="AA171" si="157">-AA108/AA5</f>
         <v>3.2931354359925787E-2</v>
       </c>
       <c r="AC171" s="149">
@@ -33603,7 +33564,7 @@
         <v>0.10690633869441817</v>
       </c>
       <c r="T172" s="149">
-        <f t="shared" ref="T172:Z172" si="158">-(T108/T58)</f>
+        <f t="shared" ref="T172:Y172" si="158">-(T108/T58)</f>
         <v>0.15058823529411763</v>
       </c>
       <c r="U172" s="149">
@@ -33664,7 +33625,7 @@
         <v>0.73139158576051777</v>
       </c>
       <c r="T173" s="149">
-        <f t="shared" ref="T173:Z173" si="160">-T108/T52</f>
+        <f t="shared" ref="T173:Y173" si="160">-T108/T52</f>
         <v>0.90140845070422537</v>
       </c>
       <c r="U173" s="149">
@@ -34447,7 +34408,7 @@
         <v>0.14167585446527012</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" ref="T193:AA195" si="171">IF(Z181=0,
+        <f t="shared" ref="AA193:AA195" si="171">IF(Z181=0,
 IF(AA181=0,0,IF(AA181&gt;0,1,-1)),
 (AA181-Z181)/ABS(Z181)
 )</f>
@@ -34667,7 +34628,7 @@
         <v>0.24629363940698232</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" ref="T197:AA198" si="181">IF(Z185=0,
+        <f t="shared" ref="AA197:AA198" si="181">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -35105,7 +35066,7 @@
       </c>
       <c r="C5" s="166">
         <f ca="1">Overview!C5</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35121,7 +35082,7 @@
       </c>
       <c r="C6" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>94705.14</v>
+        <v>91372.5</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35141,7 +35102,7 @@
       </c>
       <c r="C7" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>93921.14</v>
+        <v>90588.5</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>28</v>
@@ -35161,7 +35122,7 @@
       </c>
       <c r="C8" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>45.04299065420561</v>
+        <v>43.45794392523365</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>236</v>
@@ -35181,7 +35142,7 @@
       </c>
       <c r="C9" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>7.2113944800243974</v>
+        <v>6.9576280878316563</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>237</v>
@@ -35201,7 +35162,7 @@
       </c>
       <c r="C10" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>16.862468193384224</v>
+        <v>16.269083969465647</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35221,7 +35182,7 @@
       </c>
       <c r="C11" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>7.1608066483684052</v>
+        <v>6.9067169868862459</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35230,7 +35191,7 @@
       </c>
       <c r="C12" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>35.603161485974219</v>
+        <v>34.339840788476117</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35466,7 +35427,7 @@
       </c>
       <c r="C38" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.2201012532160346E-2</v>
+        <v>2.3010752688172043E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>263</v>
@@ -35482,7 +35443,7 @@
       </c>
       <c r="C39" s="209">
         <f ca="1">Statement!AC155</f>
-        <v>3.2543112232345572E-2</v>
+        <v>3.3730061013981232E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>265</v>
@@ -35498,7 +35459,7 @@
       </c>
       <c r="C40" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.0374304921570256E-3</v>
+        <v>1.0752688172043011E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>266</v>
@@ -35523,7 +35484,7 @@
       </c>
       <c r="C42" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0136725419549561E-3</v>
+        <v>1.0506443404744315E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35567,7 +35528,7 @@
       </c>
       <c r="F48" s="169">
         <f ca="1">Statement!AC170</f>
-        <v>8.2783257592988092E-3</v>
+        <v>8.5802621138745244E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35633,7 +35594,7 @@
       </c>
       <c r="C58" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>30.728468526930563</v>
+        <v>29.647144711226478</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
@@ -35642,7 +35603,7 @@
       </c>
       <c r="C59" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>25.769635370408675</v>
+        <v>29.655995258635148</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
@@ -35651,7 +35612,7 @@
       </c>
       <c r="C60" s="169">
         <f>Statement!AC160</f>
-        <v>0.27787768609994279</v>
+        <v>0.2328944595064692</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
@@ -35789,7 +35750,7 @@
       </c>
       <c r="I6" s="166">
         <f ca="1">Statement!AC114</f>
-        <v>240.98</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35818,7 +35779,7 @@
       </c>
       <c r="I7" s="167">
         <f ca="1">Statement!AC147</f>
-        <v>94705.14</v>
+        <v>91372.5</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35847,7 +35808,7 @@
       </c>
       <c r="I8" s="167">
         <f ca="1">Statement!AC148</f>
-        <v>93921.14</v>
+        <v>90588.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35876,7 +35837,7 @@
       </c>
       <c r="I9" s="168">
         <f ca="1">Statement!AC144</f>
-        <v>45.04299065420561</v>
+        <v>43.45794392523365</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35905,7 +35866,7 @@
       </c>
       <c r="I10" s="168">
         <f ca="1">Statement!AC145</f>
-        <v>7.2113944800243974</v>
+        <v>6.9576280878316563</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35934,7 +35895,7 @@
       </c>
       <c r="I11" s="168">
         <f ca="1">Statement!AC146</f>
-        <v>16.862468193384224</v>
+        <v>16.269083969465647</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35963,7 +35924,7 @@
       </c>
       <c r="I12" s="168">
         <f ca="1">Statement!AC149</f>
-        <v>7.1608066483684052</v>
+        <v>6.9067169868862459</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35992,7 +35953,7 @@
       </c>
       <c r="I13" s="168">
         <f ca="1">Statement!AC150</f>
-        <v>35.603161485974219</v>
+        <v>34.339840788476117</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36765,7 +36726,7 @@
       </c>
       <c r="I51" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>2.2201012532160346E-2</v>
+        <v>2.3010752688172043E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36794,7 +36755,7 @@
       </c>
       <c r="I52" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>3.2543112232345572E-2</v>
+        <v>3.3730061013981232E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36823,7 +36784,7 @@
       </c>
       <c r="I53" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>1.0374304921570256E-3</v>
+        <v>1.0752688172043011E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -36881,7 +36842,7 @@
       </c>
       <c r="I55" s="169">
         <f ca="1">Statement!AC159</f>
-        <v>1.0136725419549561E-3</v>
+        <v>1.0506443404744315E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37117,7 +37078,7 @@
       </c>
       <c r="I68" s="190">
         <f ca="1">Statement!AC170</f>
-        <v>8.2783257592988092E-3</v>
+        <v>8.5802621138745244E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37491,7 +37452,7 @@
       </c>
       <c r="I88" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>30.728468526930563</v>
+        <v>29.647144711226478</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
@@ -37520,7 +37481,7 @@
       </c>
       <c r="I89" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>25.769635370408675</v>
+        <v>29.655995258635148</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
@@ -37549,7 +37510,7 @@
       </c>
       <c r="I90" s="190">
         <f>Statement!AC160</f>
-        <v>0.27787768609994279</v>
+        <v>0.2328944595064692</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
@@ -37833,14 +37794,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="253"/>
+      <c r="F3" s="254" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37907,19 +37868,19 @@
       <c r="B7" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.31704337202199145</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.6113602391629297</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="201" t="s">
@@ -37946,19 +37907,19 @@
       <c r="B9" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>0.30897498773908777</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.60300300300300302</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="201" t="s">
@@ -37985,19 +37946,19 @@
       <c r="B11" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.33036437246963563</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.62512363996043518</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="201" t="s">
@@ -38024,19 +37985,19 @@
       <c r="B13" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>9.6505823627287851E-2</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.33400809716599189</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="201" t="s">
@@ -38063,19 +38024,19 @@
       <c r="B15" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.55205047318611988</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.90328820116054154</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="201" t="s">
@@ -38102,19 +38063,19 @@
       <c r="B17" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.53614457831325302</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.91729323308270672</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -38141,22 +38102,22 @@
       <c r="B19" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>0</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.1150895140664966E-3</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="201" t="s">
@@ -38183,22 +38144,22 @@
       <c r="B21" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.53543307086614167</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.91176470588235281</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38247,22 +38208,22 @@
       <c r="B25" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.44326412361178175</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.74591121495327106</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38290,22 +38251,22 @@
       <c r="B27" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>8.1944444444444445E-2</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.49807692307692308</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38333,22 +38294,22 @@
       <c r="B29" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="253">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.12603305785123967</v>
       </c>
-      <c r="D29" s="254"/>
-      <c r="F29" s="253">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.22747747747747749</v>
       </c>
-      <c r="G29" s="254"/>
+      <c r="G29" s="251"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -38376,22 +38337,22 @@
       <c r="B32" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="253">
+      <c r="C32" s="250">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.3956254796623177</v>
       </c>
-      <c r="D32" s="254"/>
-      <c r="F32" s="253">
+      <c r="D32" s="251"/>
+      <c r="F32" s="250">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.67758302583025831</v>
       </c>
-      <c r="G32" s="254"/>
+      <c r="G32" s="251"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -38419,25 +38380,43 @@
       <c r="B34" s="200" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="253">
+      <c r="C34" s="250">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.1976047904191617E-2</v>
       </c>
-      <c r="D34" s="254"/>
-      <c r="F34" s="253">
+      <c r="D34" s="251"/>
+      <c r="F34" s="250">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.33070866141732286</v>
       </c>
-      <c r="G34" s="254"/>
+      <c r="G34" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="C34:D34"/>
@@ -38448,24 +38427,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
